--- a/data/source/weekly/cs-en-us-pbqs.xlsx
+++ b/data/source/weekly/cs-en-us-pbqs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -199,61 +199,61 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
+    <t>***.*</t>
+  </si>
+  <si>
+    <t>Housing</t>
+  </si>
+  <si>
+    <t>Petit Larceny</t>
+  </si>
+  <si>
+    <t>Retail Theft</t>
+  </si>
+  <si>
+    <t>Misd. Assault</t>
+  </si>
+  <si>
+    <t>UCR Rape*</t>
+  </si>
+  <si>
+    <t>Other Sex Crimes</t>
+  </si>
+  <si>
+    <t>Shooting Vic.</t>
+  </si>
+  <si>
+    <t>Shooting Inc.</t>
+  </si>
+  <si>
+    <t>Hate Crimes</t>
+  </si>
+  <si>
     <t>0</t>
-  </si>
-  <si>
-    <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
-  </si>
-  <si>
-    <t>Housing</t>
-  </si>
-  <si>
-    <t>Petit Larceny</t>
-  </si>
-  <si>
-    <t>Retail Theft</t>
-  </si>
-  <si>
-    <t>Misd. Assault</t>
-  </si>
-  <si>
-    <t>UCR Rape*</t>
-  </si>
-  <si>
-    <t>Other Sex Crimes</t>
-  </si>
-  <si>
-    <t>Shooting Vic.</t>
-  </si>
-  <si>
-    <t>Shooting Inc.</t>
-  </si>
-  <si>
-    <t>Hate Crimes</t>
   </si>
   <si>
     <t>Traffic Statistics</t>
@@ -854,617 +854,617 @@
       <c r="C14" s="14">
         <v>1</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>2</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-50</v>
       </c>
       <c r="F14" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G14" s="14">
         <v>5</v>
       </c>
       <c r="H14" s="15">
-        <v>-60</v>
+        <v>-20</v>
       </c>
       <c r="I14" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J14" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K14" s="15">
-        <v>-40</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L14" s="15">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="M14" s="15">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="N14" s="15">
-        <v>-80</v>
+        <v>-76.190476190476</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C15" s="14">
         <v>3</v>
       </c>
       <c r="D15" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F15" s="14">
+        <v>11</v>
+      </c>
+      <c r="G15" s="14">
         <v>13</v>
       </c>
-      <c r="G15" s="14">
-        <v>18</v>
-      </c>
       <c r="H15" s="15">
-        <v>-27.777777777777</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I15" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J15" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K15" s="15">
-        <v>-4.545454545454</v>
+        <v>8.695652173913</v>
       </c>
       <c r="L15" s="15">
-        <v>61.538461538461</v>
+        <v>56.25</v>
       </c>
       <c r="M15" s="15">
-        <v>90.909090909090</v>
+        <v>92.307692307692</v>
       </c>
       <c r="N15" s="15">
-        <v>-46.153846153846</v>
+        <v>-43.181818181818</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C16" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D16" s="14">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E16" s="15">
-        <v>35.294117647058</v>
+        <v>-16</v>
       </c>
       <c r="F16" s="14">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G16" s="14">
         <v>80</v>
       </c>
       <c r="H16" s="15">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="I16" s="14">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="J16" s="14">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="K16" s="15">
-        <v>-1.709401709401</v>
+        <v>-4.225352112676</v>
       </c>
       <c r="L16" s="15">
-        <v>-20.138888888888</v>
+        <v>-15</v>
       </c>
       <c r="M16" s="15">
-        <v>-56.766917293233</v>
+        <v>-55.263157894736</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.902050113895</v>
+        <v>-86.627335299901</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C17" s="14">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D17" s="14">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="E17" s="15">
-        <v>-10.909090909090</v>
+        <v>2.272727272727</v>
       </c>
       <c r="F17" s="14">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G17" s="14">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="H17" s="15">
-        <v>-1.477832512315</v>
+        <v>6.451612903225</v>
       </c>
       <c r="I17" s="14">
-        <v>283</v>
+        <v>334</v>
       </c>
       <c r="J17" s="14">
-        <v>296</v>
+        <v>340</v>
       </c>
       <c r="K17" s="15">
-        <v>-4.391891891891</v>
+        <v>-1.764705882352</v>
       </c>
       <c r="L17" s="15">
-        <v>-5.980066445182</v>
+        <v>-5.113636363636</v>
       </c>
       <c r="M17" s="15">
-        <v>86.184210526315</v>
+        <v>90.857142857142</v>
       </c>
       <c r="N17" s="15">
-        <v>-19.373219373219</v>
+        <v>-19.128329297820</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C18" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" s="14">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="F18" s="14">
         <v>45</v>
       </c>
       <c r="G18" s="14">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H18" s="15">
-        <v>-40.789473684210</v>
+        <v>-36.619718309859</v>
       </c>
       <c r="I18" s="14">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J18" s="14">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="K18" s="15">
-        <v>-32.456140350877</v>
+        <v>-34.074074074074</v>
       </c>
       <c r="L18" s="15">
-        <v>-23</v>
+        <v>-29.921259842519</v>
       </c>
       <c r="M18" s="15">
-        <v>-63.507109004739</v>
+        <v>-63.374485596707</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.443572129538</v>
+        <v>-92.334194659776</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" s="14">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="D19" s="14">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="E19" s="15">
-        <v>-27.692307692307</v>
+        <v>27.450980392156</v>
       </c>
       <c r="F19" s="14">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G19" s="14">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="H19" s="15">
-        <v>-8.333333333333</v>
+        <v>-7.296137339055</v>
       </c>
       <c r="I19" s="14">
-        <v>311</v>
+        <v>381</v>
       </c>
       <c r="J19" s="14">
-        <v>332</v>
+        <v>383</v>
       </c>
       <c r="K19" s="15">
-        <v>-6.325301204819</v>
+        <v>-0.522193211488</v>
       </c>
       <c r="L19" s="15">
-        <v>-17.506631299734</v>
+        <v>-13.800904977375</v>
       </c>
       <c r="M19" s="15">
-        <v>4.013377926421</v>
+        <v>14.759036144578</v>
       </c>
       <c r="N19" s="15">
-        <v>-46.837606837606</v>
+        <v>-43.970588235294</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C20" s="14">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D20" s="14">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E20" s="15">
-        <v>5.555555555555</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="F20" s="14">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="G20" s="14">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H20" s="15">
-        <v>-4.878048780487</v>
+        <v>-14.516129032258</v>
       </c>
       <c r="I20" s="14">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="J20" s="14">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="K20" s="15">
-        <v>-8.426966292134</v>
+        <v>-9.178743961352</v>
       </c>
       <c r="L20" s="15">
-        <v>-22.009569377990</v>
+        <v>-21.991701244813</v>
       </c>
       <c r="M20" s="15">
-        <v>-18.905472636815</v>
+        <v>-15.315315315315</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.439703153988</v>
+        <v>-92.446765769385</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C21" s="17">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D21" s="17">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="E21" s="18">
-        <v>-8.064516129032</v>
+        <v>-0.578034682080</v>
       </c>
       <c r="F21" s="17">
-        <v>679</v>
+        <v>664</v>
       </c>
       <c r="G21" s="17">
-        <v>745</v>
+        <v>712</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.859060402684</v>
+        <v>-6.741573033707</v>
       </c>
       <c r="I21" s="17">
-        <v>973</v>
+        <v>1158</v>
       </c>
       <c r="J21" s="17">
-        <v>1064</v>
+        <v>1237</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.552631578947</v>
+        <v>-6.386418755052</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.243902439024</v>
+        <v>-13.710879284649</v>
       </c>
       <c r="M21" s="18">
-        <v>-14.947552447552</v>
+        <v>-10.440835266821</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.705929010509</v>
+        <v>-80.120171673819</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="F22" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
+        <v>200</v>
+      </c>
+      <c r="I22" s="14">
+        <v>24</v>
+      </c>
+      <c r="J22" s="14">
+        <v>6</v>
+      </c>
+      <c r="K22" s="15">
         <v>300</v>
       </c>
-      <c r="I22" s="14">
-        <v>19</v>
-      </c>
-      <c r="J22" s="14">
-        <v>5</v>
-      </c>
-      <c r="K22" s="15">
-        <v>280</v>
-      </c>
       <c r="L22" s="15">
-        <v>35.714285714285</v>
+        <v>50</v>
       </c>
       <c r="M22" s="15">
-        <v>111.111111111111</v>
+        <v>118.181818181818</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" s="14">
         <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>-50</v>
+        <v>-80</v>
       </c>
       <c r="F23" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G23" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H23" s="15">
-        <v>-15.384615384615</v>
+        <v>-40</v>
       </c>
       <c r="I23" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J23" s="14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K23" s="15">
-        <v>-5.263157894736</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="L23" s="15">
-        <v>-30.769230769230</v>
+        <v>-36.666666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>-30.769230769230</v>
+        <v>-34.482758620689</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" s="14">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="D24" s="14">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="E24" s="15">
-        <v>-14.124293785310</v>
+        <v>4.761904761904</v>
       </c>
       <c r="F24" s="14">
-        <v>699</v>
+        <v>638</v>
       </c>
       <c r="G24" s="14">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="H24" s="15">
-        <v>2.043795620437</v>
+        <v>-5.481481481481</v>
       </c>
       <c r="I24" s="14">
-        <v>952</v>
+        <v>1126</v>
       </c>
       <c r="J24" s="14">
-        <v>897</v>
+        <v>1065</v>
       </c>
       <c r="K24" s="15">
-        <v>6.131549609810</v>
+        <v>5.727699530516</v>
       </c>
       <c r="L24" s="15">
-        <v>5.543237250554</v>
+        <v>2.925045703839</v>
       </c>
       <c r="M24" s="15">
-        <v>55.810147299509</v>
+        <v>60.857142857142</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" s="14">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D25" s="14">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E25" s="15">
-        <v>-16.455696202531</v>
+        <v>-14.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>301</v>
+        <v>262</v>
       </c>
       <c r="G25" s="14">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="H25" s="15">
-        <v>9.854014598540</v>
+        <v>-11.186440677966</v>
       </c>
       <c r="I25" s="14">
-        <v>380</v>
+        <v>446</v>
       </c>
       <c r="J25" s="14">
-        <v>353</v>
+        <v>428</v>
       </c>
       <c r="K25" s="15">
-        <v>7.648725212464</v>
+        <v>4.205607476635</v>
       </c>
       <c r="L25" s="15">
-        <v>3.260869565217</v>
+        <v>2.528735632183</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="14">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D26" s="14">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E26" s="15">
-        <v>-2.325581395348</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="F26" s="14">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="G26" s="14">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H26" s="15">
-        <v>-9.439528023598</v>
+        <v>-13.473053892215</v>
       </c>
       <c r="I26" s="14">
-        <v>425</v>
+        <v>504</v>
       </c>
       <c r="J26" s="14">
-        <v>465</v>
+        <v>557</v>
       </c>
       <c r="K26" s="15">
-        <v>-8.602150537634</v>
+        <v>-9.515260323159</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.494382022471</v>
+        <v>-5.440900562851</v>
       </c>
       <c r="M26" s="15">
-        <v>-7.205240174672</v>
+        <v>-5.794392523364</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D27" s="14">
         <v>4</v>
       </c>
       <c r="E27" s="15">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G27" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>5.555555555555</v>
       </c>
       <c r="I27" s="14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J27" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K27" s="15">
-        <v>11.538461538461</v>
+        <v>13.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>31.818181818181</v>
+        <v>25.925925925925</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" s="14">
+        <v>9</v>
+      </c>
+      <c r="D28" s="14">
         <v>13</v>
       </c>
-      <c r="D28" s="14">
-        <v>10</v>
-      </c>
       <c r="E28" s="15">
-        <v>30</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="F28" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G28" s="14">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H28" s="15">
-        <v>10</v>
+        <v>2.702702702702</v>
       </c>
       <c r="I28" s="14">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="J28" s="14">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="K28" s="15">
-        <v>8.888888888888</v>
+        <v>-1.724137931034</v>
       </c>
       <c r="L28" s="15">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29" s="14">
         <v>1</v>
@@ -1476,36 +1476,36 @@
         <v>0</v>
       </c>
       <c r="F29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H29" s="15">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J29" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K29" s="15">
-        <v>-80</v>
+        <v>-75</v>
       </c>
       <c r="L29" s="15">
-        <v>-75</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="M29" s="15">
-        <v>-75</v>
+        <v>-73.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.161290322580</v>
+        <v>-94.285714285714</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C30" s="14">
         <v>1</v>
@@ -1517,72 +1517,72 @@
         <v>0</v>
       </c>
       <c r="F30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H30" s="15">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K30" s="15">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L30" s="15">
-        <v>-70</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="M30" s="15">
-        <v>-72.727272727272</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.736842105263</v>
+        <v>-93.75</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="14">
+        <v>1</v>
+      </c>
+      <c r="D31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F31" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G31" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H31" s="15">
-        <v>50</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I31" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J31" s="14">
         <v>6</v>
       </c>
       <c r="K31" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L31" s="15">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1608,7 +1608,7 @@
         <v>40</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D33" s="14">
         <v>1</v>
@@ -1617,19 +1617,19 @@
         <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="G33" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H33" s="15">
         <v>-100</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="J33" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K33" s="15">
         <v>-100</v>
@@ -1638,10 +1638,10 @@
         <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C40" s="14">
         <v>341</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C41" s="14">
         <v>8056</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C42" s="14">
         <v>3941</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C43" s="14">
         <v>11976</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C44" s="14">
         <v>7856</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C45" s="14">
         <v>21758</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C46" s="17">
         <v>54089</v>

--- a/data/source/weekly/cs-en-us-pbqs.xlsx
+++ b/data/source/weekly/cs-en-us-pbqs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -247,13 +247,13 @@
     <t>Shooting Vic.</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>Shooting Inc.</t>
   </si>
   <si>
     <t>Hate Crimes</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>Traffic Statistics</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -855,37 +855,37 @@
         <v>1</v>
       </c>
       <c r="D14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F14" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" s="14">
         <v>5</v>
       </c>
       <c r="H14" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I14" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J14" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K14" s="15">
-        <v>-28.571428571428</v>
+        <v>-25</v>
       </c>
       <c r="L14" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M14" s="15">
-        <v>25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N14" s="15">
-        <v>-76.190476190476</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>20</v>
       </c>
       <c r="C15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E15" s="15">
-        <v>200</v>
+        <v>-50</v>
       </c>
       <c r="F15" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G15" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H15" s="15">
-        <v>-15.384615384615</v>
+        <v>-25</v>
       </c>
       <c r="I15" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J15" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K15" s="15">
-        <v>8.695652173913</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="L15" s="15">
-        <v>56.25</v>
+        <v>44.444444444444</v>
       </c>
       <c r="M15" s="15">
-        <v>92.307692307692</v>
+        <v>85.714285714285</v>
       </c>
       <c r="N15" s="15">
-        <v>-43.181818181818</v>
+        <v>-45.833333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>21</v>
       </c>
       <c r="C16" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D16" s="14">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E16" s="15">
-        <v>-16</v>
+        <v>35.294117647058</v>
       </c>
       <c r="F16" s="14">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G16" s="14">
         <v>80</v>
       </c>
       <c r="H16" s="15">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="I16" s="14">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="J16" s="14">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="K16" s="15">
-        <v>-4.225352112676</v>
+        <v>-0.628930817610</v>
       </c>
       <c r="L16" s="15">
-        <v>-15</v>
+        <v>-11.731843575419</v>
       </c>
       <c r="M16" s="15">
-        <v>-55.263157894736</v>
+        <v>-53.665689149560</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.627335299901</v>
+        <v>-86.343993085566</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>22</v>
       </c>
       <c r="C17" s="14">
+        <v>54</v>
+      </c>
+      <c r="D17" s="14">
         <v>45</v>
       </c>
-      <c r="D17" s="14">
-        <v>44</v>
-      </c>
       <c r="E17" s="15">
-        <v>2.272727272727</v>
+        <v>20</v>
       </c>
       <c r="F17" s="14">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="G17" s="14">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="H17" s="15">
-        <v>6.451612903225</v>
+        <v>9.424083769633</v>
       </c>
       <c r="I17" s="14">
-        <v>334</v>
+        <v>391</v>
       </c>
       <c r="J17" s="14">
-        <v>340</v>
+        <v>385</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.764705882352</v>
+        <v>1.558441558441</v>
       </c>
       <c r="L17" s="15">
-        <v>-5.113636363636</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="M17" s="15">
-        <v>90.857142857142</v>
+        <v>81.860465116279</v>
       </c>
       <c r="N17" s="15">
-        <v>-19.128329297820</v>
+        <v>-15.550755939524</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>23</v>
       </c>
       <c r="C18" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D18" s="14">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E18" s="15">
-        <v>-47.619047619047</v>
+        <v>-10</v>
       </c>
       <c r="F18" s="14">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G18" s="14">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="H18" s="15">
-        <v>-36.619718309859</v>
+        <v>-31.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="J18" s="14">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="K18" s="15">
-        <v>-34.074074074074</v>
+        <v>-33.103448275862</v>
       </c>
       <c r="L18" s="15">
-        <v>-29.921259842519</v>
+        <v>-28.676470588235</v>
       </c>
       <c r="M18" s="15">
-        <v>-63.374485596707</v>
+        <v>-63.670411985018</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.334194659776</v>
+        <v>-92.701279157261</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>24</v>
       </c>
       <c r="C19" s="14">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D19" s="14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E19" s="15">
-        <v>27.450980392156</v>
+        <v>20</v>
       </c>
       <c r="F19" s="14">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="G19" s="14">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="H19" s="15">
-        <v>-7.296137339055</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="I19" s="14">
-        <v>381</v>
+        <v>449</v>
       </c>
       <c r="J19" s="14">
-        <v>383</v>
+        <v>438</v>
       </c>
       <c r="K19" s="15">
-        <v>-0.522193211488</v>
+        <v>2.511415525114</v>
       </c>
       <c r="L19" s="15">
-        <v>-13.800904977375</v>
+        <v>-11.787819253438</v>
       </c>
       <c r="M19" s="15">
-        <v>14.759036144578</v>
+        <v>13.383838383838</v>
       </c>
       <c r="N19" s="15">
-        <v>-43.970588235294</v>
+        <v>-43.020304568527</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>25</v>
       </c>
       <c r="C20" s="14">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D20" s="14">
         <v>29</v>
       </c>
       <c r="E20" s="15">
-        <v>-10.344827586206</v>
+        <v>44.827586206896</v>
       </c>
       <c r="F20" s="14">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="G20" s="14">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H20" s="15">
-        <v>-14.516129032258</v>
+        <v>-6.4</v>
       </c>
       <c r="I20" s="14">
-        <v>188</v>
+        <v>229</v>
       </c>
       <c r="J20" s="14">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="K20" s="15">
-        <v>-9.178743961352</v>
+        <v>-2.966101694915</v>
       </c>
       <c r="L20" s="15">
-        <v>-21.991701244813</v>
+        <v>-17.625899280575</v>
       </c>
       <c r="M20" s="15">
-        <v>-15.315315315315</v>
+        <v>-4.979253112033</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.446765769385</v>
+        <v>-91.916696081892</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>26</v>
       </c>
       <c r="C21" s="17">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="D21" s="17">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="E21" s="18">
-        <v>-0.578034682080</v>
+        <v>22.360248447205</v>
       </c>
       <c r="F21" s="17">
-        <v>664</v>
+        <v>690</v>
       </c>
       <c r="G21" s="17">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H21" s="18">
-        <v>-6.741573033707</v>
+        <v>-2.953586497890</v>
       </c>
       <c r="I21" s="17">
-        <v>1158</v>
+        <v>1356</v>
       </c>
       <c r="J21" s="17">
-        <v>1237</v>
+        <v>1398</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.386418755052</v>
+        <v>-3.004291845493</v>
       </c>
       <c r="L21" s="18">
-        <v>-13.710879284649</v>
+        <v>-11.488250652741</v>
       </c>
       <c r="M21" s="18">
-        <v>-10.440835266821</v>
+        <v>-8.563722184760</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.120171673819</v>
+        <v>-79.584462511291</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>27</v>
       </c>
       <c r="C22" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>400</v>
+        <v>-50</v>
       </c>
       <c r="F22" s="14">
         <v>15</v>
       </c>
       <c r="G22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H22" s="15">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="I22" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J22" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K22" s="15">
-        <v>300</v>
+        <v>212.5</v>
       </c>
       <c r="L22" s="15">
-        <v>50</v>
+        <v>38.888888888888</v>
       </c>
       <c r="M22" s="15">
-        <v>118.181818181818</v>
+        <v>78.571428571428</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>28</v>
@@ -1221,37 +1221,37 @@
         <v>29</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G23" s="14">
         <v>15</v>
       </c>
       <c r="H23" s="15">
-        <v>-40</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="I23" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J23" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K23" s="15">
-        <v>-20.833333333333</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="L23" s="15">
-        <v>-36.666666666666</v>
+        <v>-37.142857142857</v>
       </c>
       <c r="M23" s="15">
-        <v>-34.482758620689</v>
+        <v>-31.25</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>28</v>
@@ -1262,37 +1262,37 @@
         <v>30</v>
       </c>
       <c r="C24" s="14">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="D24" s="14">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="E24" s="15">
-        <v>4.761904761904</v>
+        <v>6.081081081081</v>
       </c>
       <c r="F24" s="14">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="G24" s="14">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="H24" s="15">
-        <v>-5.481481481481</v>
+        <v>-5.697151424287</v>
       </c>
       <c r="I24" s="14">
-        <v>1126</v>
+        <v>1286</v>
       </c>
       <c r="J24" s="14">
-        <v>1065</v>
+        <v>1213</v>
       </c>
       <c r="K24" s="15">
-        <v>5.727699530516</v>
+        <v>6.018136850783</v>
       </c>
       <c r="L24" s="15">
-        <v>2.925045703839</v>
+        <v>2.144559173947</v>
       </c>
       <c r="M24" s="15">
-        <v>60.857142857142</v>
+        <v>60.75</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>28</v>
@@ -1303,34 +1303,34 @@
         <v>31</v>
       </c>
       <c r="C25" s="14">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D25" s="14">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E25" s="15">
-        <v>-14.666666666666</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="F25" s="14">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="G25" s="14">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="H25" s="15">
-        <v>-11.186440677966</v>
+        <v>-16.107382550335</v>
       </c>
       <c r="I25" s="14">
-        <v>446</v>
+        <v>498</v>
       </c>
       <c r="J25" s="14">
-        <v>428</v>
+        <v>491</v>
       </c>
       <c r="K25" s="15">
-        <v>4.205607476635</v>
+        <v>1.425661914460</v>
       </c>
       <c r="L25" s="15">
-        <v>2.528735632183</v>
+        <v>0.809716599190</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>28</v>
@@ -1344,37 +1344,37 @@
         <v>32</v>
       </c>
       <c r="C26" s="14">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D26" s="14">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="E26" s="15">
-        <v>-13.043478260869</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="G26" s="14">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="H26" s="15">
-        <v>-13.473053892215</v>
+        <v>-8.588957055214</v>
       </c>
       <c r="I26" s="14">
-        <v>504</v>
+        <v>579</v>
       </c>
       <c r="J26" s="14">
-        <v>557</v>
+        <v>635</v>
       </c>
       <c r="K26" s="15">
-        <v>-9.515260323159</v>
+        <v>-8.818897637795</v>
       </c>
       <c r="L26" s="15">
-        <v>-5.440900562851</v>
+        <v>-5.237315875613</v>
       </c>
       <c r="M26" s="15">
-        <v>-5.794392523364</v>
+        <v>-3.015075376884</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>28</v>
@@ -1385,34 +1385,34 @@
         <v>33</v>
       </c>
       <c r="C27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E27" s="15">
         <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G27" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H27" s="15">
-        <v>5.555555555555</v>
+        <v>5.882352941176</v>
       </c>
       <c r="I27" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J27" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K27" s="15">
-        <v>13.333333333333</v>
+        <v>8.571428571428</v>
       </c>
       <c r="L27" s="15">
-        <v>25.925925925925</v>
+        <v>18.75</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>28</v>
@@ -1426,34 +1426,34 @@
         <v>34</v>
       </c>
       <c r="C28" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D28" s="14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E28" s="15">
-        <v>-30.769230769230</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F28" s="14">
+        <v>32</v>
+      </c>
+      <c r="G28" s="14">
         <v>38</v>
       </c>
-      <c r="G28" s="14">
-        <v>37</v>
-      </c>
       <c r="H28" s="15">
-        <v>2.702702702702</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="I28" s="14">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J28" s="14">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="K28" s="15">
-        <v>-1.724137931034</v>
+        <v>-1.5625</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>28</v>
@@ -1469,114 +1469,114 @@
       <c r="C29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>0</v>
+      <c r="D29" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="F29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G29" s="14">
         <v>4</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J29" s="14">
         <v>16</v>
       </c>
       <c r="K29" s="15">
-        <v>-75</v>
+        <v>-68.75</v>
       </c>
       <c r="L29" s="15">
-        <v>-69.230769230769</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="M29" s="15">
-        <v>-73.333333333333</v>
+        <v>-80.769230769230</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.285714285714</v>
+        <v>-93.421052631578</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0</v>
+      <c r="D30" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="F30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G30" s="14">
         <v>4</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30" s="14">
         <v>7</v>
       </c>
       <c r="K30" s="15">
-        <v>-42.857142857142</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L30" s="15">
-        <v>-63.636363636363</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="M30" s="15">
-        <v>-69.230769230769</v>
+        <v>-75</v>
       </c>
       <c r="N30" s="15">
-        <v>-93.75</v>
+        <v>-92.753623188405</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C31" s="14">
         <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E31" s="13" t="s">
         <v>28</v>
       </c>
       <c r="F31" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G31" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>166.666666666667</v>
+        <v>250</v>
       </c>
       <c r="I31" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J31" s="14">
         <v>6</v>
       </c>
       <c r="K31" s="15">
-        <v>50</v>
+        <v>83.333333333333</v>
       </c>
       <c r="L31" s="15">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>28</v>
@@ -1608,34 +1608,34 @@
         <v>40</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+        <v>36</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G33" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H33" s="15">
         <v>-100</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>38</v>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="14">
         <v>5</v>
       </c>
       <c r="K33" s="15">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="L33" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>28</v>

--- a/data/source/weekly/cs-en-us-pbqs.xlsx
+++ b/data/source/weekly/cs-en-us-pbqs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -199,6 +199,9 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -245,9 +248,6 @@
   </si>
   <si>
     <t>Shooting Vic.</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>Shooting Inc.</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -851,544 +851,544 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14" s="14">
         <v>5</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="I14" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J14" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K14" s="15">
-        <v>-25</v>
+        <v>-30</v>
       </c>
       <c r="L14" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M14" s="15">
-        <v>-33.333333333333</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="N14" s="15">
-        <v>-75</v>
+        <v>-72</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
         <v>2</v>
       </c>
       <c r="D15" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
         <v>9</v>
       </c>
       <c r="G15" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H15" s="15">
-        <v>-25</v>
+        <v>-10</v>
       </c>
       <c r="I15" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J15" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K15" s="15">
-        <v>-3.703703703703</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="L15" s="15">
-        <v>44.444444444444</v>
+        <v>12.5</v>
       </c>
       <c r="M15" s="15">
-        <v>85.714285714285</v>
+        <v>80</v>
       </c>
       <c r="N15" s="15">
-        <v>-45.833333333333</v>
+        <v>-48.076923076923</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D16" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E16" s="15">
-        <v>35.294117647058</v>
+        <v>-6.25</v>
       </c>
       <c r="F16" s="14">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G16" s="14">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H16" s="15">
-        <v>6.25</v>
+        <v>10.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="J16" s="14">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="K16" s="15">
-        <v>-0.628930817610</v>
+        <v>0</v>
       </c>
       <c r="L16" s="15">
-        <v>-11.731843575419</v>
+        <v>-16.267942583732</v>
       </c>
       <c r="M16" s="15">
-        <v>-53.665689149560</v>
+        <v>-52.316076294277</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.343993085566</v>
+        <v>-86.517719568567</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D17" s="14">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="E17" s="15">
-        <v>20</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="F17" s="14">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="G17" s="14">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="H17" s="15">
-        <v>9.424083769633</v>
+        <v>-4.285714285714</v>
       </c>
       <c r="I17" s="14">
-        <v>391</v>
+        <v>443</v>
       </c>
       <c r="J17" s="14">
-        <v>385</v>
+        <v>451</v>
       </c>
       <c r="K17" s="15">
-        <v>1.558441558441</v>
+        <v>-1.773835920177</v>
       </c>
       <c r="L17" s="15">
-        <v>-4.166666666666</v>
+        <v>-7.127882599580</v>
       </c>
       <c r="M17" s="15">
-        <v>81.860465116279</v>
+        <v>77.2</v>
       </c>
       <c r="N17" s="15">
-        <v>-15.550755939524</v>
+        <v>-15.619047619047</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D18" s="14">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E18" s="15">
-        <v>-10</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F18" s="14">
         <v>41</v>
       </c>
       <c r="G18" s="14">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H18" s="15">
-        <v>-31.666666666666</v>
+        <v>-33.870967741935</v>
       </c>
       <c r="I18" s="14">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="J18" s="14">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="K18" s="15">
-        <v>-33.103448275862</v>
+        <v>-34.939759036144</v>
       </c>
       <c r="L18" s="15">
-        <v>-28.676470588235</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-63.670411985018</v>
+        <v>-65.048543689320</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.701279157261</v>
+        <v>-92.627986348122</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="D19" s="14">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E19" s="15">
         <v>20</v>
       </c>
       <c r="F19" s="14">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="G19" s="14">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="H19" s="15">
-        <v>-5.882352941176</v>
+        <v>8.796296296296</v>
       </c>
       <c r="I19" s="14">
-        <v>449</v>
+        <v>503</v>
       </c>
       <c r="J19" s="14">
-        <v>438</v>
+        <v>483</v>
       </c>
       <c r="K19" s="15">
-        <v>2.511415525114</v>
+        <v>4.140786749482</v>
       </c>
       <c r="L19" s="15">
-        <v>-11.787819253438</v>
+        <v>-13.275862068965</v>
       </c>
       <c r="M19" s="15">
-        <v>13.383838383838</v>
+        <v>13.033707865168</v>
       </c>
       <c r="N19" s="15">
-        <v>-43.020304568527</v>
+        <v>-44.048943270300</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="D20" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E20" s="15">
-        <v>44.827586206896</v>
+        <v>-40.625</v>
       </c>
       <c r="F20" s="14">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G20" s="14">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H20" s="15">
-        <v>-6.4</v>
+        <v>-3.174603174603</v>
       </c>
       <c r="I20" s="14">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="J20" s="14">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="K20" s="15">
-        <v>-2.966101694915</v>
+        <v>-7.835820895522</v>
       </c>
       <c r="L20" s="15">
-        <v>-17.625899280575</v>
+        <v>-17.940199335548</v>
       </c>
       <c r="M20" s="15">
-        <v>-4.979253112033</v>
+        <v>-7.490636704119</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.916696081892</v>
+        <v>-92.274006881451</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>197</v>
+        <v>152</v>
       </c>
       <c r="D21" s="17">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="E21" s="18">
-        <v>22.360248447205</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="F21" s="17">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="G21" s="17">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.953586497890</v>
+        <v>-1.278409090909</v>
       </c>
       <c r="I21" s="17">
-        <v>1356</v>
+        <v>1510</v>
       </c>
       <c r="J21" s="17">
-        <v>1398</v>
+        <v>1582</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.004291845493</v>
+        <v>-4.551201011378</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.488250652741</v>
+        <v>-14.058053500284</v>
       </c>
       <c r="M21" s="18">
-        <v>-8.563722184760</v>
+        <v>-9.254807692307</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.584462511291</v>
+        <v>-79.761426082294</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C22" s="14">
+        <v>2</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
       <c r="E22" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F22" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G22" s="14">
         <v>6</v>
       </c>
       <c r="H22" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="I22" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J22" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K22" s="15">
-        <v>212.5</v>
+        <v>200</v>
       </c>
       <c r="L22" s="15">
-        <v>38.888888888888</v>
+        <v>12.5</v>
       </c>
       <c r="M22" s="15">
-        <v>78.571428571428</v>
+        <v>28.571428571428</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-87.5</v>
       </c>
       <c r="F23" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H23" s="15">
-        <v>-46.666666666666</v>
+        <v>-72.222222222222</v>
       </c>
       <c r="I23" s="14">
         <v>22</v>
       </c>
       <c r="J23" s="14">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="K23" s="15">
-        <v>-18.518518518518</v>
+        <v>-37.142857142857</v>
       </c>
       <c r="L23" s="15">
+        <v>-43.589743589743</v>
+      </c>
+      <c r="M23" s="15">
         <v>-37.142857142857</v>
       </c>
-      <c r="M23" s="15">
-        <v>-31.25</v>
-      </c>
       <c r="N23" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>157</v>
+        <v>118</v>
       </c>
       <c r="D24" s="14">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E24" s="15">
-        <v>6.081081081081</v>
+        <v>-22.875816993464</v>
       </c>
       <c r="F24" s="14">
-        <v>629</v>
+        <v>611</v>
       </c>
       <c r="G24" s="14">
-        <v>667</v>
+        <v>646</v>
       </c>
       <c r="H24" s="15">
-        <v>-5.697151424287</v>
+        <v>-5.417956656346</v>
       </c>
       <c r="I24" s="14">
-        <v>1286</v>
+        <v>1407</v>
       </c>
       <c r="J24" s="14">
-        <v>1213</v>
+        <v>1366</v>
       </c>
       <c r="K24" s="15">
-        <v>6.018136850783</v>
+        <v>3.001464128843</v>
       </c>
       <c r="L24" s="15">
-        <v>2.144559173947</v>
+        <v>-3.761969904240</v>
       </c>
       <c r="M24" s="15">
-        <v>60.75</v>
+        <v>59.162895927601</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D25" s="14">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E25" s="15">
-        <v>-19.047619047619</v>
+        <v>-35.483870967741</v>
       </c>
       <c r="F25" s="14">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="G25" s="14">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="H25" s="15">
-        <v>-16.107382550335</v>
+        <v>-19.713261648745</v>
       </c>
       <c r="I25" s="14">
-        <v>498</v>
+        <v>538</v>
       </c>
       <c r="J25" s="14">
-        <v>491</v>
+        <v>553</v>
       </c>
       <c r="K25" s="15">
-        <v>1.425661914460</v>
+        <v>-2.712477396021</v>
       </c>
       <c r="L25" s="15">
-        <v>0.809716599190</v>
+        <v>-4.946996466431</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="D26" s="14">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-15.584415584415</v>
       </c>
       <c r="F26" s="14">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G26" s="14">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="H26" s="15">
-        <v>-8.588957055214</v>
+        <v>-10.210210210210</v>
       </c>
       <c r="I26" s="14">
-        <v>579</v>
+        <v>636</v>
       </c>
       <c r="J26" s="14">
-        <v>635</v>
+        <v>712</v>
       </c>
       <c r="K26" s="15">
-        <v>-8.818897637795</v>
+        <v>-10.674157303370</v>
       </c>
       <c r="L26" s="15">
-        <v>-5.237315875613</v>
+        <v>-8.882521489971</v>
       </c>
       <c r="M26" s="15">
-        <v>-3.015075376884</v>
+        <v>-6.607929515418</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D27" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
         <v>0</v>
@@ -1397,110 +1397,110 @@
         <v>18</v>
       </c>
       <c r="G27" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H27" s="15">
-        <v>5.882352941176</v>
+        <v>20</v>
       </c>
       <c r="I27" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J27" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K27" s="15">
-        <v>8.571428571428</v>
+        <v>8.108108108108</v>
       </c>
       <c r="L27" s="15">
-        <v>18.75</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="14">
+        <v>8</v>
+      </c>
+      <c r="D28" s="14">
+        <v>13</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-38.461538461538</v>
+      </c>
+      <c r="F28" s="14">
         <v>34</v>
       </c>
-      <c r="C28" s="14">
-        <v>5</v>
-      </c>
-      <c r="D28" s="14">
-        <v>6</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-16.666666666666</v>
-      </c>
-      <c r="F28" s="14">
-        <v>32</v>
-      </c>
       <c r="G28" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H28" s="15">
-        <v>-15.789473684210</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="I28" s="14">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J28" s="14">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="K28" s="15">
-        <v>-1.5625</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L28" s="15">
-        <v>-4.545454545454</v>
+        <v>-4.109589041095</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29" s="14">
         <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F29" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G29" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="I29" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J29" s="14">
         <v>16</v>
       </c>
       <c r="K29" s="15">
-        <v>-68.75</v>
+        <v>-62.5</v>
       </c>
       <c r="L29" s="15">
-        <v>-64.285714285714</v>
+        <v>-60</v>
       </c>
       <c r="M29" s="15">
-        <v>-80.769230769230</v>
+        <v>-80.645161290322</v>
       </c>
       <c r="N29" s="15">
-        <v>-93.421052631578</v>
+        <v>-92.771084337349</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1511,60 +1511,60 @@
         <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F30" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G30" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="I30" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J30" s="14">
         <v>7</v>
       </c>
       <c r="K30" s="15">
-        <v>-28.571428571428</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L30" s="15">
-        <v>-58.333333333333</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="M30" s="15">
-        <v>-75</v>
+        <v>-73.913043478260</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.753623188405</v>
+        <v>-92.105263157894</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F31" s="14">
-        <v>7</v>
-      </c>
-      <c r="G31" s="14">
-        <v>2</v>
-      </c>
-      <c r="H31" s="15">
-        <v>250</v>
+        <v>3</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="I31" s="14">
         <v>11</v>
@@ -1576,13 +1576,13 @@
         <v>83.333333333333</v>
       </c>
       <c r="L31" s="15">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1608,19 +1608,19 @@
         <v>40</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="G33" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H33" s="15">
         <v>-100</v>
@@ -1635,13 +1635,13 @@
         <v>-80</v>
       </c>
       <c r="L33" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>341</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>8056</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>3941</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>11976</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>7856</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>21758</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>54089</v>

--- a/data/source/weekly/cs-en-us-pbqs.xlsx
+++ b/data/source/weekly/cs-en-us-pbqs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -854,20 +854,20 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>2</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14" s="14">
         <v>5</v>
       </c>
       <c r="H14" s="15">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="I14" s="14">
         <v>7</v>
@@ -885,335 +885,335 @@
         <v>-36.363636363636</v>
       </c>
       <c r="N14" s="15">
-        <v>-72</v>
+        <v>-76.666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E15" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="F15" s="14">
+        <v>14</v>
+      </c>
+      <c r="G15" s="14">
+        <v>13</v>
+      </c>
+      <c r="H15" s="15">
+        <v>7.692307692307</v>
+      </c>
+      <c r="I15" s="14">
+        <v>35</v>
+      </c>
+      <c r="J15" s="14">
+        <v>35</v>
+      </c>
+      <c r="K15" s="15">
         <v>0</v>
       </c>
-      <c r="F15" s="14">
-        <v>9</v>
-      </c>
-      <c r="G15" s="14">
-        <v>10</v>
-      </c>
-      <c r="H15" s="15">
-        <v>-10</v>
-      </c>
-      <c r="I15" s="14">
-        <v>27</v>
-      </c>
-      <c r="J15" s="14">
-        <v>29</v>
-      </c>
-      <c r="K15" s="15">
-        <v>-6.896551724137</v>
-      </c>
       <c r="L15" s="15">
-        <v>12.5</v>
+        <v>20.689655172413</v>
       </c>
       <c r="M15" s="15">
-        <v>80</v>
+        <v>59.090909090909</v>
       </c>
       <c r="N15" s="15">
-        <v>-48.076923076923</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D16" s="14">
         <v>16</v>
       </c>
       <c r="E16" s="15">
-        <v>-6.25</v>
+        <v>31.25</v>
       </c>
       <c r="F16" s="14">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G16" s="14">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H16" s="15">
-        <v>10.666666666666</v>
+        <v>8.108108108108</v>
       </c>
       <c r="I16" s="14">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="J16" s="14">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="K16" s="15">
-        <v>0</v>
+        <v>2.094240837696</v>
       </c>
       <c r="L16" s="15">
-        <v>-16.267942583732</v>
+        <v>-18.75</v>
       </c>
       <c r="M16" s="15">
-        <v>-52.316076294277</v>
+        <v>-52.439024390243</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.517719568567</v>
+        <v>-86.570247933884</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D17" s="14">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E17" s="15">
-        <v>-24.242424242424</v>
+        <v>-28.070175438596</v>
       </c>
       <c r="F17" s="14">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="G17" s="14">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H17" s="15">
-        <v>-4.285714285714</v>
+        <v>-9.433962264150</v>
       </c>
       <c r="I17" s="14">
-        <v>443</v>
+        <v>484</v>
       </c>
       <c r="J17" s="14">
-        <v>451</v>
+        <v>508</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.773835920177</v>
+        <v>-4.724409448818</v>
       </c>
       <c r="L17" s="15">
-        <v>-7.127882599580</v>
+        <v>-10.536044362292</v>
       </c>
       <c r="M17" s="15">
-        <v>77.2</v>
+        <v>74.729241877256</v>
       </c>
       <c r="N17" s="15">
-        <v>-15.619047619047</v>
+        <v>-16.981132075471</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" s="14">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E18" s="15">
-        <v>-42.857142857142</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G18" s="14">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H18" s="15">
-        <v>-33.870967741935</v>
+        <v>-35.820895522388</v>
       </c>
       <c r="I18" s="14">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="J18" s="14">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="K18" s="15">
-        <v>-34.939759036144</v>
+        <v>-33.149171270718</v>
       </c>
       <c r="L18" s="15">
-        <v>-33.333333333333</v>
+        <v>-33.149171270718</v>
       </c>
       <c r="M18" s="15">
-        <v>-65.048543689320</v>
+        <v>-64.411764705882</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.627986348122</v>
+        <v>-92.512376237623</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="D19" s="14">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="E19" s="15">
-        <v>20</v>
+        <v>19.354838709677</v>
       </c>
       <c r="F19" s="14">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="G19" s="14">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H19" s="15">
-        <v>8.796296296296</v>
+        <v>22.065727699530</v>
       </c>
       <c r="I19" s="14">
-        <v>503</v>
+        <v>579</v>
       </c>
       <c r="J19" s="14">
-        <v>483</v>
+        <v>545</v>
       </c>
       <c r="K19" s="15">
-        <v>4.140786749482</v>
+        <v>6.238532110091</v>
       </c>
       <c r="L19" s="15">
-        <v>-13.275862068965</v>
+        <v>-8.962264150943</v>
       </c>
       <c r="M19" s="15">
-        <v>13.033707865168</v>
+        <v>17.922606924643</v>
       </c>
       <c r="N19" s="15">
-        <v>-44.048943270300</v>
+        <v>-41.277890466531</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="14">
+        <v>35</v>
+      </c>
+      <c r="D20" s="14">
         <v>26</v>
       </c>
-      <c r="C20" s="14">
-        <v>19</v>
-      </c>
-      <c r="D20" s="14">
-        <v>32</v>
-      </c>
       <c r="E20" s="15">
-        <v>-40.625</v>
+        <v>34.615384615384</v>
       </c>
       <c r="F20" s="14">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G20" s="14">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H20" s="15">
-        <v>-3.174603174603</v>
+        <v>4.310344827586</v>
       </c>
       <c r="I20" s="14">
-        <v>247</v>
+        <v>282</v>
       </c>
       <c r="J20" s="14">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="K20" s="15">
-        <v>-7.835820895522</v>
+        <v>-4.081632653061</v>
       </c>
       <c r="L20" s="15">
-        <v>-17.940199335548</v>
+        <v>-12.962962962963</v>
       </c>
       <c r="M20" s="15">
-        <v>-7.490636704119</v>
+        <v>-0.704225352112</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.274006881451</v>
+        <v>-91.979522184300</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="D21" s="17">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E21" s="18">
-        <v>-17.391304347826</v>
+        <v>5.494505494505</v>
       </c>
       <c r="F21" s="17">
-        <v>695</v>
+        <v>713</v>
       </c>
       <c r="G21" s="17">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="H21" s="18">
-        <v>-1.278409090909</v>
+        <v>1.857142857142</v>
       </c>
       <c r="I21" s="17">
-        <v>1510</v>
+        <v>1703</v>
       </c>
       <c r="J21" s="17">
-        <v>1582</v>
+        <v>1764</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.551201011378</v>
+        <v>-3.458049886621</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.058053500284</v>
+        <v>-12.890025575447</v>
       </c>
       <c r="M21" s="18">
-        <v>-9.254807692307</v>
+        <v>-7.193460490463</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.761426082294</v>
+        <v>-79.330015778613</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D22" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E22" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F22" s="14">
         <v>12</v>
       </c>
       <c r="G22" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H22" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I22" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J22" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K22" s="15">
-        <v>200</v>
+        <v>138.461538461538</v>
       </c>
       <c r="L22" s="15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>28.571428571428</v>
+        <v>40.909090909090</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
         <v>8</v>
       </c>
       <c r="E23" s="15">
-        <v>-87.5</v>
+        <v>-62.5</v>
       </c>
       <c r="F23" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G23" s="14">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H23" s="15">
-        <v>-72.222222222222</v>
+        <v>-62.5</v>
       </c>
       <c r="I23" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J23" s="14">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K23" s="15">
-        <v>-37.142857142857</v>
+        <v>-37.209302325581</v>
       </c>
       <c r="L23" s="15">
-        <v>-43.589743589743</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M23" s="15">
-        <v>-37.142857142857</v>
+        <v>-28.947368421052</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>118</v>
+        <v>205</v>
       </c>
       <c r="D24" s="14">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E24" s="15">
-        <v>-22.875816993464</v>
+        <v>44.366197183098</v>
       </c>
       <c r="F24" s="14">
+        <v>657</v>
+      </c>
+      <c r="G24" s="14">
         <v>611</v>
       </c>
-      <c r="G24" s="14">
-        <v>646</v>
-      </c>
       <c r="H24" s="15">
-        <v>-5.417956656346</v>
+        <v>7.528641571194</v>
       </c>
       <c r="I24" s="14">
-        <v>1407</v>
+        <v>1611</v>
       </c>
       <c r="J24" s="14">
-        <v>1366</v>
+        <v>1508</v>
       </c>
       <c r="K24" s="15">
-        <v>3.001464128843</v>
+        <v>6.830238726790</v>
       </c>
       <c r="L24" s="15">
-        <v>-3.761969904240</v>
+        <v>-1.588271227855</v>
       </c>
       <c r="M24" s="15">
-        <v>59.162895927601</v>
+        <v>61.746987951807</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D25" s="14">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="E25" s="15">
-        <v>-35.483870967741</v>
+        <v>62.790697674418</v>
       </c>
       <c r="F25" s="14">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G25" s="14">
-        <v>279</v>
+        <v>243</v>
       </c>
       <c r="H25" s="15">
-        <v>-19.713261648745</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="I25" s="14">
-        <v>538</v>
+        <v>607</v>
       </c>
       <c r="J25" s="14">
-        <v>553</v>
+        <v>596</v>
       </c>
       <c r="K25" s="15">
-        <v>-2.712477396021</v>
+        <v>1.845637583892</v>
       </c>
       <c r="L25" s="15">
-        <v>-4.946996466431</v>
+        <v>-5.15625</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="D26" s="14">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="E26" s="15">
-        <v>-15.584415584415</v>
+        <v>9.574468085106</v>
       </c>
       <c r="F26" s="14">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="G26" s="14">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="H26" s="15">
-        <v>-10.210210210210</v>
+        <v>-6.158357771261</v>
       </c>
       <c r="I26" s="14">
-        <v>636</v>
+        <v>739</v>
       </c>
       <c r="J26" s="14">
-        <v>712</v>
+        <v>806</v>
       </c>
       <c r="K26" s="15">
-        <v>-10.674157303370</v>
+        <v>-8.312655086848</v>
       </c>
       <c r="L26" s="15">
-        <v>-8.882521489971</v>
+        <v>-8.877928483353</v>
       </c>
       <c r="M26" s="15">
-        <v>-6.607929515418</v>
+        <v>-5.859872611464</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F27" s="14">
         <v>18</v>
       </c>
       <c r="G27" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H27" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="J27" s="14">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K27" s="15">
-        <v>8.108108108108</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>2.127659574468</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,63 +1426,63 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D28" s="14">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>-38.461538461538</v>
+        <v>333.333333333333</v>
       </c>
       <c r="F28" s="14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G28" s="14">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H28" s="15">
-        <v>-19.047619047619</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="J28" s="14">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K28" s="15">
-        <v>-9.090909090909</v>
+        <v>3.75</v>
       </c>
       <c r="L28" s="15">
-        <v>-4.109589041095</v>
+        <v>6.410256410256</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I29" s="14">
         <v>6</v>
@@ -1497,33 +1497,33 @@
         <v>-60</v>
       </c>
       <c r="M29" s="15">
-        <v>-80.645161290322</v>
+        <v>-81.25</v>
       </c>
       <c r="N29" s="15">
-        <v>-92.771084337349</v>
+        <v>-93.548387096774</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I30" s="14">
         <v>6</v>
@@ -1538,10 +1538,10 @@
         <v>-53.846153846153</v>
       </c>
       <c r="M30" s="15">
-        <v>-73.913043478260</v>
+        <v>-75</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.105263157894</v>
+        <v>-92.857142857142</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,16 +1555,16 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>11</v>
@@ -1576,13 +1576,13 @@
         <v>83.333333333333</v>
       </c>
       <c r="L31" s="15">
-        <v>450</v>
+        <v>266.666666666667</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,13 +1614,13 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G33" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="15">
         <v>-100</v>
@@ -1638,10 +1638,10 @@
         <v>-80</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>341</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>8056</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>3941</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>11976</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>7856</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>21758</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>54089</v>

--- a/data/source/weekly/cs-en-us-pbqs.xlsx
+++ b/data/source/weekly/cs-en-us-pbqs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -864,28 +864,28 @@
         <v>3</v>
       </c>
       <c r="G14" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H14" s="15">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="I14" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J14" s="14">
         <v>10</v>
       </c>
       <c r="K14" s="15">
-        <v>-30</v>
+        <v>-20</v>
       </c>
       <c r="L14" s="15">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="M14" s="15">
-        <v>-36.363636363636</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N14" s="15">
-        <v>-76.666666666666</v>
+        <v>-74.193548387096</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D15" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
-        <v>33.333333333333</v>
+        <v>250</v>
       </c>
       <c r="F15" s="14">
+        <v>19</v>
+      </c>
+      <c r="G15" s="14">
         <v>14</v>
       </c>
-      <c r="G15" s="14">
-        <v>13</v>
-      </c>
       <c r="H15" s="15">
-        <v>7.692307692307</v>
+        <v>35.714285714285</v>
       </c>
       <c r="I15" s="14">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J15" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>13.513513513513</v>
       </c>
       <c r="L15" s="15">
-        <v>20.689655172413</v>
+        <v>27.272727272727</v>
       </c>
       <c r="M15" s="15">
-        <v>59.090909090909</v>
+        <v>68</v>
       </c>
       <c r="N15" s="15">
-        <v>-37.5</v>
+        <v>-37.313432835820</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D16" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E16" s="15">
-        <v>31.25</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G16" s="14">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="H16" s="15">
-        <v>8.108108108108</v>
+        <v>15.151515151515</v>
       </c>
       <c r="I16" s="14">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="J16" s="14">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="K16" s="15">
-        <v>2.094240837696</v>
+        <v>1.442307692307</v>
       </c>
       <c r="L16" s="15">
-        <v>-18.75</v>
+        <v>-19.771863117870</v>
       </c>
       <c r="M16" s="15">
-        <v>-52.439024390243</v>
+        <v>-53.626373626373</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.570247933884</v>
+        <v>-86.729559748427</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="D17" s="14">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E17" s="15">
-        <v>-28.070175438596</v>
+        <v>-1.724137931034</v>
       </c>
       <c r="F17" s="14">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="G17" s="14">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="H17" s="15">
-        <v>-9.433962264150</v>
+        <v>-10.176991150442</v>
       </c>
       <c r="I17" s="14">
-        <v>484</v>
+        <v>542</v>
       </c>
       <c r="J17" s="14">
-        <v>508</v>
+        <v>566</v>
       </c>
       <c r="K17" s="15">
-        <v>-4.724409448818</v>
+        <v>-4.240282685512</v>
       </c>
       <c r="L17" s="15">
-        <v>-10.536044362292</v>
+        <v>-8.600337268128</v>
       </c>
       <c r="M17" s="15">
-        <v>74.729241877256</v>
+        <v>81.270903010033</v>
       </c>
       <c r="N17" s="15">
-        <v>-16.981132075471</v>
+        <v>-16.615384615384</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D18" s="14">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E18" s="15">
-        <v>-13.333333333333</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="F18" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G18" s="14">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="H18" s="15">
-        <v>-35.820895522388</v>
+        <v>-41.772151898734</v>
       </c>
       <c r="I18" s="14">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="J18" s="14">
-        <v>181</v>
+        <v>214</v>
       </c>
       <c r="K18" s="15">
-        <v>-33.149171270718</v>
+        <v>-37.383177570093</v>
       </c>
       <c r="L18" s="15">
-        <v>-33.149171270718</v>
+        <v>-33</v>
       </c>
       <c r="M18" s="15">
-        <v>-64.411764705882</v>
+        <v>-64.550264550264</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.512376237623</v>
+        <v>-92.437923250564</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D19" s="14">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E19" s="15">
-        <v>19.354838709677</v>
+        <v>40</v>
       </c>
       <c r="F19" s="14">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="G19" s="14">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="H19" s="15">
-        <v>22.065727699530</v>
+        <v>25.345622119815</v>
       </c>
       <c r="I19" s="14">
-        <v>579</v>
+        <v>658</v>
       </c>
       <c r="J19" s="14">
-        <v>545</v>
+        <v>600</v>
       </c>
       <c r="K19" s="15">
-        <v>6.238532110091</v>
+        <v>9.666666666666</v>
       </c>
       <c r="L19" s="15">
-        <v>-8.962264150943</v>
+        <v>-7.062146892655</v>
       </c>
       <c r="M19" s="15">
-        <v>17.922606924643</v>
+        <v>23.452157598499</v>
       </c>
       <c r="N19" s="15">
-        <v>-41.277890466531</v>
+        <v>-39.298892988929</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D20" s="14">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E20" s="15">
-        <v>34.615384615384</v>
+        <v>3.030303030303</v>
       </c>
       <c r="F20" s="14">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="G20" s="14">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H20" s="15">
-        <v>4.310344827586</v>
+        <v>6.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="J20" s="14">
-        <v>294</v>
+        <v>327</v>
       </c>
       <c r="K20" s="15">
-        <v>-4.081632653061</v>
+        <v>-3.363914373088</v>
       </c>
       <c r="L20" s="15">
-        <v>-12.962962962963</v>
+        <v>-11.731843575419</v>
       </c>
       <c r="M20" s="15">
-        <v>-0.704225352112</v>
+        <v>0</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.979522184300</v>
+        <v>-91.781534460338</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="D21" s="17">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="E21" s="18">
-        <v>5.494505494505</v>
+        <v>2.020202020202</v>
       </c>
       <c r="F21" s="17">
-        <v>713</v>
+        <v>747</v>
       </c>
       <c r="G21" s="17">
-        <v>700</v>
+        <v>725</v>
       </c>
       <c r="H21" s="18">
-        <v>1.857142857142</v>
+        <v>3.034482758620</v>
       </c>
       <c r="I21" s="17">
-        <v>1703</v>
+        <v>1911</v>
       </c>
       <c r="J21" s="17">
-        <v>1764</v>
+        <v>1962</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.458049886621</v>
+        <v>-2.599388379204</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.890025575447</v>
+        <v>-11.486799444187</v>
       </c>
       <c r="M21" s="18">
-        <v>-7.193460490463</v>
+        <v>-5.302279484638</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.330015778613</v>
+        <v>-78.858280783272</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>4</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G22" s="14">
         <v>8</v>
       </c>
       <c r="H22" s="15">
-        <v>50</v>
+        <v>-12.5</v>
       </c>
       <c r="I22" s="14">
         <v>31</v>
       </c>
       <c r="J22" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K22" s="15">
-        <v>138.461538461538</v>
+        <v>121.428571428571</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>-3.125</v>
       </c>
       <c r="M22" s="15">
-        <v>40.909090909090</v>
+        <v>19.230769230769</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>-62.5</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G23" s="14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H23" s="15">
-        <v>-62.5</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J23" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K23" s="15">
-        <v>-37.209302325581</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="L23" s="15">
-        <v>-30.769230769230</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M23" s="15">
-        <v>-28.947368421052</v>
+        <v>-26.829268292682</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="D24" s="14">
-        <v>142</v>
+        <v>174</v>
       </c>
       <c r="E24" s="15">
-        <v>44.366197183098</v>
+        <v>5.172413793103</v>
       </c>
       <c r="F24" s="14">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G24" s="14">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="H24" s="15">
-        <v>7.528641571194</v>
+        <v>6.320907617504</v>
       </c>
       <c r="I24" s="14">
-        <v>1611</v>
+        <v>1787</v>
       </c>
       <c r="J24" s="14">
-        <v>1508</v>
+        <v>1682</v>
       </c>
       <c r="K24" s="15">
-        <v>6.830238726790</v>
+        <v>6.242568370986</v>
       </c>
       <c r="L24" s="15">
-        <v>-1.588271227855</v>
+        <v>-0.832408435072</v>
       </c>
       <c r="M24" s="15">
-        <v>61.746987951807</v>
+        <v>63.494967978042</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D25" s="14">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="E25" s="15">
-        <v>62.790697674418</v>
+        <v>-19.277108433734</v>
       </c>
       <c r="F25" s="14">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G25" s="14">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="H25" s="15">
-        <v>-7.407407407407</v>
+        <v>-10.756972111553</v>
       </c>
       <c r="I25" s="14">
-        <v>607</v>
+        <v>671</v>
       </c>
       <c r="J25" s="14">
-        <v>596</v>
+        <v>679</v>
       </c>
       <c r="K25" s="15">
-        <v>1.845637583892</v>
+        <v>-1.178203240058</v>
       </c>
       <c r="L25" s="15">
-        <v>-5.15625</v>
+        <v>-5.890603085554</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="D26" s="14">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="E26" s="15">
-        <v>9.574468085106</v>
+        <v>63.380281690140</v>
       </c>
       <c r="F26" s="14">
+        <v>360</v>
+      </c>
+      <c r="G26" s="14">
         <v>320</v>
       </c>
-      <c r="G26" s="14">
-        <v>341</v>
-      </c>
       <c r="H26" s="15">
-        <v>-6.158357771261</v>
+        <v>12.5</v>
       </c>
       <c r="I26" s="14">
-        <v>739</v>
+        <v>855</v>
       </c>
       <c r="J26" s="14">
-        <v>806</v>
+        <v>877</v>
       </c>
       <c r="K26" s="15">
-        <v>-8.312655086848</v>
+        <v>-2.508551881413</v>
       </c>
       <c r="L26" s="15">
-        <v>-8.877928483353</v>
+        <v>-5.420353982300</v>
       </c>
       <c r="M26" s="15">
-        <v>-5.859872611464</v>
+        <v>-2.508551881413</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,31 +1388,31 @@
         <v>8</v>
       </c>
       <c r="D27" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E27" s="15">
-        <v>14.285714285714</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F27" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G27" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>29.411764705882</v>
       </c>
       <c r="I27" s="14">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="J27" s="14">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K27" s="15">
-        <v>9.090909090909</v>
+        <v>19.148936170212</v>
       </c>
       <c r="L27" s="15">
-        <v>2.127659574468</v>
+        <v>5.660377358490</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>13</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E28" s="15">
-        <v>333.333333333333</v>
+        <v>62.5</v>
       </c>
       <c r="F28" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G28" s="14">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>26.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J28" s="14">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K28" s="15">
-        <v>3.75</v>
+        <v>7.954545454545</v>
       </c>
       <c r="L28" s="15">
-        <v>6.410256410256</v>
+        <v>20.253164556962</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,14 +1466,14 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0</v>
       </c>
       <c r="F29" s="14">
         <v>3</v>
@@ -1485,36 +1485,36 @@
         <v>200</v>
       </c>
       <c r="I29" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J29" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K29" s="15">
-        <v>-62.5</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="L29" s="15">
-        <v>-60</v>
+        <v>-56.25</v>
       </c>
       <c r="M29" s="15">
-        <v>-81.25</v>
+        <v>-81.578947368421</v>
       </c>
       <c r="N29" s="15">
-        <v>-93.548387096774</v>
+        <v>-93</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
       </c>
       <c r="F30" s="14">
         <v>3</v>
@@ -1526,30 +1526,30 @@
         <v>200</v>
       </c>
       <c r="I30" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J30" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K30" s="15">
-        <v>-14.285714285714</v>
+        <v>-12.5</v>
       </c>
       <c r="L30" s="15">
-        <v>-53.846153846153</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-75</v>
+        <v>-75.862068965517</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.857142857142</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1567,16 +1567,16 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J31" s="14">
         <v>6</v>
       </c>
       <c r="K31" s="15">
-        <v>83.333333333333</v>
+        <v>100</v>
       </c>
       <c r="L31" s="15">
-        <v>266.666666666667</v>
+        <v>300</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>3</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,26 +1616,26 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
+      <c r="F33" s="14">
+        <v>3</v>
+      </c>
+      <c r="G33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J33" s="14">
         <v>5</v>
       </c>
       <c r="K33" s="15">
-        <v>-80</v>
+        <v>-20</v>
       </c>
       <c r="L33" s="15">
-        <v>-80</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-pbqs.xlsx
+++ b/data/source/weekly/cs-en-us-pbqs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -861,13 +861,13 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I14" s="14">
         <v>8</v>
@@ -879,13 +879,13 @@
         <v>-20</v>
       </c>
       <c r="L14" s="15">
-        <v>100</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M14" s="15">
-        <v>-33.333333333333</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="N14" s="15">
-        <v>-74.193548387096</v>
+        <v>-77.142857142857</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E15" s="15">
-        <v>250</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F15" s="14">
         <v>19</v>
       </c>
       <c r="G15" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H15" s="15">
-        <v>35.714285714285</v>
+        <v>18.75</v>
       </c>
       <c r="I15" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J15" s="14">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K15" s="15">
-        <v>13.513513513513</v>
+        <v>2.325581395348</v>
       </c>
       <c r="L15" s="15">
-        <v>27.272727272727</v>
+        <v>15.789473684210</v>
       </c>
       <c r="M15" s="15">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="N15" s="15">
-        <v>-37.313432835820</v>
+        <v>-39.726027397260</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-25.925925925925</v>
       </c>
       <c r="F16" s="14">
+        <v>73</v>
+      </c>
+      <c r="G16" s="14">
         <v>76</v>
       </c>
-      <c r="G16" s="14">
-        <v>66</v>
-      </c>
       <c r="H16" s="15">
-        <v>15.151515151515</v>
+        <v>-3.947368421052</v>
       </c>
       <c r="I16" s="14">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="J16" s="14">
-        <v>208</v>
+        <v>235</v>
       </c>
       <c r="K16" s="15">
-        <v>1.442307692307</v>
+        <v>-0.851063829787</v>
       </c>
       <c r="L16" s="15">
-        <v>-19.771863117870</v>
+        <v>-16.785714285714</v>
       </c>
       <c r="M16" s="15">
-        <v>-53.626373626373</v>
+        <v>-52.351738241308</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.729559748427</v>
+        <v>-86.500579374275</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D17" s="14">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E17" s="15">
-        <v>-1.724137931034</v>
+        <v>12.962962962963</v>
       </c>
       <c r="F17" s="14">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="G17" s="14">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="H17" s="15">
-        <v>-10.176991150442</v>
+        <v>-10.212765957446</v>
       </c>
       <c r="I17" s="14">
-        <v>542</v>
+        <v>609</v>
       </c>
       <c r="J17" s="14">
-        <v>566</v>
+        <v>620</v>
       </c>
       <c r="K17" s="15">
-        <v>-4.240282685512</v>
+        <v>-1.774193548387</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.600337268128</v>
+        <v>-6.163328197226</v>
       </c>
       <c r="M17" s="15">
-        <v>81.270903010033</v>
+        <v>83.433734939759</v>
       </c>
       <c r="N17" s="15">
-        <v>-16.615384615384</v>
+        <v>-15.062761506276</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D18" s="14">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E18" s="15">
-        <v>-72.727272727272</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="F18" s="14">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G18" s="14">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="H18" s="15">
-        <v>-41.772151898734</v>
+        <v>-45.652173913043</v>
       </c>
       <c r="I18" s="14">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="J18" s="14">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="K18" s="15">
-        <v>-37.383177570093</v>
+        <v>-36.708860759493</v>
       </c>
       <c r="L18" s="15">
-        <v>-33</v>
+        <v>-30.875576036866</v>
       </c>
       <c r="M18" s="15">
-        <v>-64.550264550264</v>
+        <v>-65.357967667436</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.437923250564</v>
+        <v>-92.167101827676</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D19" s="14">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E19" s="15">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F19" s="14">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G19" s="14">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H19" s="15">
-        <v>25.345622119815</v>
+        <v>26.886792452830</v>
       </c>
       <c r="I19" s="14">
-        <v>658</v>
+        <v>723</v>
       </c>
       <c r="J19" s="14">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="K19" s="15">
-        <v>9.666666666666</v>
+        <v>11.230769230769</v>
       </c>
       <c r="L19" s="15">
-        <v>-7.062146892655</v>
+        <v>-6.468305304010</v>
       </c>
       <c r="M19" s="15">
-        <v>23.452157598499</v>
+        <v>25.739130434782</v>
       </c>
       <c r="N19" s="15">
-        <v>-39.298892988929</v>
+        <v>-40.689089417555</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D20" s="14">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E20" s="15">
-        <v>3.030303030303</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F20" s="14">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G20" s="14">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="H20" s="15">
-        <v>6.666666666666</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I20" s="14">
-        <v>316</v>
+        <v>359</v>
       </c>
       <c r="J20" s="14">
-        <v>327</v>
+        <v>376</v>
       </c>
       <c r="K20" s="15">
-        <v>-3.363914373088</v>
+        <v>-4.521276595744</v>
       </c>
       <c r="L20" s="15">
-        <v>-11.731843575419</v>
+        <v>-9.798994974874</v>
       </c>
       <c r="M20" s="15">
-        <v>0</v>
+        <v>2.571428571428</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.781534460338</v>
+        <v>-91.380552220888</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D21" s="17">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E21" s="18">
-        <v>2.020202020202</v>
+        <v>-1.913875598086</v>
       </c>
       <c r="F21" s="17">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="G21" s="17">
-        <v>725</v>
+        <v>773</v>
       </c>
       <c r="H21" s="18">
-        <v>3.034482758620</v>
+        <v>-2.587322121604</v>
       </c>
       <c r="I21" s="17">
-        <v>1911</v>
+        <v>2126</v>
       </c>
       <c r="J21" s="17">
-        <v>1962</v>
+        <v>2171</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.599388379204</v>
+        <v>-2.072777521879</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.486799444187</v>
+        <v>-9.991532599491</v>
       </c>
       <c r="M21" s="18">
-        <v>-5.302279484638</v>
+        <v>-4.104645917907</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.858280783272</v>
+        <v>-78.416243654822</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="14">
+        <v>2</v>
+      </c>
+      <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G22" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H22" s="15">
-        <v>-12.5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I22" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J22" s="14">
         <v>14</v>
       </c>
       <c r="K22" s="15">
-        <v>121.428571428571</v>
+        <v>135.714285714286</v>
       </c>
       <c r="L22" s="15">
-        <v>-3.125</v>
+        <v>3.125</v>
       </c>
       <c r="M22" s="15">
-        <v>19.230769230769</v>
+        <v>10</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F23" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G23" s="14">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I23" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J23" s="14">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="K23" s="15">
-        <v>-34.782608695652</v>
+        <v>-40</v>
       </c>
       <c r="L23" s="15">
-        <v>-28.571428571428</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>-26.829268292682</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>183</v>
+        <v>145</v>
       </c>
       <c r="D24" s="14">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="E24" s="15">
-        <v>5.172413793103</v>
+        <v>-25.641025641025</v>
       </c>
       <c r="F24" s="14">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="G24" s="14">
-        <v>617</v>
+        <v>664</v>
       </c>
       <c r="H24" s="15">
-        <v>6.320907617504</v>
+        <v>-2.710843373493</v>
       </c>
       <c r="I24" s="14">
-        <v>1787</v>
+        <v>1931</v>
       </c>
       <c r="J24" s="14">
-        <v>1682</v>
+        <v>1877</v>
       </c>
       <c r="K24" s="15">
-        <v>6.242568370986</v>
+        <v>2.876931273308</v>
       </c>
       <c r="L24" s="15">
-        <v>-0.832408435072</v>
+        <v>-2.671370967741</v>
       </c>
       <c r="M24" s="15">
-        <v>63.494967978042</v>
+        <v>61.319966583124</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D25" s="14">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E25" s="15">
-        <v>-19.277108433734</v>
+        <v>-32.954545454545</v>
       </c>
       <c r="F25" s="14">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="G25" s="14">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="H25" s="15">
-        <v>-10.756972111553</v>
+        <v>-15.217391304347</v>
       </c>
       <c r="I25" s="14">
-        <v>671</v>
+        <v>729</v>
       </c>
       <c r="J25" s="14">
-        <v>679</v>
+        <v>767</v>
       </c>
       <c r="K25" s="15">
-        <v>-1.178203240058</v>
+        <v>-4.954367666232</v>
       </c>
       <c r="L25" s="15">
-        <v>-5.890603085554</v>
+        <v>-7.133757961783</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="D26" s="14">
         <v>71</v>
       </c>
       <c r="E26" s="15">
-        <v>63.380281690140</v>
+        <v>21.126760563380</v>
       </c>
       <c r="F26" s="14">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="G26" s="14">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="H26" s="15">
-        <v>12.5</v>
+        <v>20.127795527156</v>
       </c>
       <c r="I26" s="14">
-        <v>855</v>
+        <v>944</v>
       </c>
       <c r="J26" s="14">
-        <v>877</v>
+        <v>948</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.508551881413</v>
+        <v>-0.421940928270</v>
       </c>
       <c r="L26" s="15">
-        <v>-5.420353982300</v>
+        <v>-4.356636271529</v>
       </c>
       <c r="M26" s="15">
-        <v>-2.508551881413</v>
+        <v>-2.176165803108</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D27" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E27" s="15">
-        <v>166.666666666667</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F27" s="14">
         <v>22</v>
       </c>
       <c r="G27" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H27" s="15">
-        <v>29.411764705882</v>
+        <v>15.789473684210</v>
       </c>
       <c r="I27" s="14">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J27" s="14">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="K27" s="15">
-        <v>19.148936170212</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L27" s="15">
-        <v>5.660377358490</v>
+        <v>1.694915254237</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D28" s="14">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E28" s="15">
-        <v>62.5</v>
+        <v>6.666666666666</v>
       </c>
       <c r="F28" s="14">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G28" s="14">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H28" s="15">
-        <v>26.666666666666</v>
+        <v>30.769230769230</v>
       </c>
       <c r="I28" s="14">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="J28" s="14">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="K28" s="15">
-        <v>7.954545454545</v>
+        <v>8.737864077669</v>
       </c>
       <c r="L28" s="15">
-        <v>20.253164556962</v>
+        <v>31.764705882352</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>0</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
         <v>3</v>
@@ -1485,22 +1485,22 @@
         <v>200</v>
       </c>
       <c r="I29" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J29" s="14">
         <v>17</v>
       </c>
       <c r="K29" s="15">
-        <v>-58.823529411764</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="L29" s="15">
-        <v>-56.25</v>
+        <v>-61.904761904761</v>
       </c>
       <c r="M29" s="15">
-        <v>-81.578947368421</v>
+        <v>-80.487804878048</v>
       </c>
       <c r="N29" s="15">
-        <v>-93</v>
+        <v>-92.792792792792</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>3</v>
@@ -1526,30 +1526,30 @@
         <v>200</v>
       </c>
       <c r="I30" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J30" s="14">
         <v>8</v>
       </c>
       <c r="K30" s="15">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="M30" s="15">
-        <v>-75.862068965517</v>
+        <v>-75</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.307692307692</v>
+        <v>-92</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1567,16 +1567,16 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J31" s="14">
         <v>6</v>
       </c>
       <c r="K31" s="15">
-        <v>100</v>
+        <v>83.333333333333</v>
       </c>
       <c r="L31" s="15">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>3</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1635,7 +1635,7 @@
         <v>-20</v>
       </c>
       <c r="L33" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-pbqs.xlsx
+++ b/data/source/weekly/cs-en-us-pbqs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -199,61 +199,61 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
+    <t>***.*</t>
+  </si>
+  <si>
+    <t>Housing</t>
+  </si>
+  <si>
+    <t>Petit Larceny</t>
+  </si>
+  <si>
+    <t>Retail Theft</t>
+  </si>
+  <si>
+    <t>Misd. Assault</t>
+  </si>
+  <si>
+    <t>UCR Rape*</t>
+  </si>
+  <si>
+    <t>Other Sex Crimes</t>
+  </si>
+  <si>
+    <t>Shooting Vic.</t>
+  </si>
+  <si>
+    <t>Shooting Inc.</t>
+  </si>
+  <si>
+    <t>Hate Crimes</t>
+  </si>
+  <si>
     <t>0</t>
-  </si>
-  <si>
-    <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
-  </si>
-  <si>
-    <t>Housing</t>
-  </si>
-  <si>
-    <t>Petit Larceny</t>
-  </si>
-  <si>
-    <t>Retail Theft</t>
-  </si>
-  <si>
-    <t>Misd. Assault</t>
-  </si>
-  <si>
-    <t>UCR Rape*</t>
-  </si>
-  <si>
-    <t>Other Sex Crimes</t>
-  </si>
-  <si>
-    <t>Shooting Vic.</t>
-  </si>
-  <si>
-    <t>Shooting Inc.</t>
-  </si>
-  <si>
-    <t>Hate Crimes</t>
   </si>
   <si>
     <t>Traffic Statistics</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -851,738 +851,738 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="C14" s="14">
+        <v>1</v>
+      </c>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>0</v>
       </c>
       <c r="F14" s="14">
+        <v>2</v>
+      </c>
+      <c r="G14" s="14">
         <v>1</v>
       </c>
-      <c r="G14" s="14">
-        <v>2</v>
-      </c>
       <c r="H14" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="I14" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J14" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K14" s="15">
-        <v>-20</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L14" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="M14" s="15">
-        <v>-38.461538461538</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="N14" s="15">
-        <v>-77.142857142857</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="14">
+        <v>6</v>
+      </c>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>200</v>
+      </c>
+      <c r="F15" s="14">
         <v>22</v>
-      </c>
-      <c r="C15" s="14">
-        <v>2</v>
-      </c>
-      <c r="D15" s="14">
-        <v>6</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F15" s="14">
-        <v>19</v>
       </c>
       <c r="G15" s="14">
         <v>16</v>
       </c>
       <c r="H15" s="15">
-        <v>18.75</v>
+        <v>37.5</v>
       </c>
       <c r="I15" s="14">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J15" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K15" s="15">
-        <v>2.325581395348</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L15" s="15">
-        <v>15.789473684210</v>
+        <v>21.951219512195</v>
       </c>
       <c r="M15" s="15">
-        <v>76</v>
+        <v>85.185185185185</v>
       </c>
       <c r="N15" s="15">
-        <v>-39.726027397260</v>
+        <v>-38.271604938271</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C16" s="14">
         <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E16" s="15">
-        <v>-25.925925925925</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="F16" s="14">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G16" s="14">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H16" s="15">
-        <v>-3.947368421052</v>
+        <v>-1.234567901234</v>
       </c>
       <c r="I16" s="14">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="J16" s="14">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="K16" s="15">
-        <v>-0.851063829787</v>
+        <v>-0.390625</v>
       </c>
       <c r="L16" s="15">
-        <v>-16.785714285714</v>
+        <v>-16.393442622950</v>
       </c>
       <c r="M16" s="15">
-        <v>-52.351738241308</v>
+        <v>-51.886792452830</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.500579374275</v>
+        <v>-86.319742489270</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C17" s="14">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D17" s="14">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="E17" s="15">
-        <v>12.962962962963</v>
+        <v>32.5</v>
       </c>
       <c r="F17" s="14">
         <v>211</v>
       </c>
       <c r="G17" s="14">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="H17" s="15">
-        <v>-10.212765957446</v>
+        <v>0.476190476190</v>
       </c>
       <c r="I17" s="14">
-        <v>609</v>
+        <v>661</v>
       </c>
       <c r="J17" s="14">
-        <v>620</v>
+        <v>661</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.774193548387</v>
+        <v>0</v>
       </c>
       <c r="L17" s="15">
-        <v>-6.163328197226</v>
+        <v>-7.032348804500</v>
       </c>
       <c r="M17" s="15">
-        <v>83.433734939759</v>
+        <v>80.601092896174</v>
       </c>
       <c r="N17" s="15">
-        <v>-15.062761506276</v>
+        <v>-17.167919799498</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C18" s="14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D18" s="14">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E18" s="15">
-        <v>-34.782608695652</v>
+        <v>-30</v>
       </c>
       <c r="F18" s="14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G18" s="14">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="H18" s="15">
-        <v>-45.652173913043</v>
+        <v>-40.594059405940</v>
       </c>
       <c r="I18" s="14">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="J18" s="14">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="K18" s="15">
-        <v>-36.708860759493</v>
+        <v>-35.205992509363</v>
       </c>
       <c r="L18" s="15">
-        <v>-30.875576036866</v>
+        <v>-27.004219409282</v>
       </c>
       <c r="M18" s="15">
-        <v>-65.357967667436</v>
+        <v>-62.309368191721</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.167101827676</v>
+        <v>-91.742243436754</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" s="14">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D19" s="14">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="E19" s="15">
-        <v>30</v>
+        <v>-11.594202898550</v>
       </c>
       <c r="F19" s="14">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G19" s="14">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="H19" s="15">
-        <v>26.886792452830</v>
+        <v>14.406779661016</v>
       </c>
       <c r="I19" s="14">
-        <v>723</v>
+        <v>783</v>
       </c>
       <c r="J19" s="14">
-        <v>650</v>
+        <v>719</v>
       </c>
       <c r="K19" s="15">
-        <v>11.230769230769</v>
+        <v>8.901251738525</v>
       </c>
       <c r="L19" s="15">
-        <v>-6.468305304010</v>
+        <v>-5.434782608695</v>
       </c>
       <c r="M19" s="15">
-        <v>25.739130434782</v>
+        <v>22.152886115444</v>
       </c>
       <c r="N19" s="15">
-        <v>-40.689089417555</v>
+        <v>-41.304347826087</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C20" s="14">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D20" s="14">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E20" s="15">
-        <v>-14.285714285714</v>
+        <v>-27.5</v>
       </c>
       <c r="F20" s="14">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="G20" s="14">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H20" s="15">
-        <v>-7.142857142857</v>
+        <v>-5.405405405405</v>
       </c>
       <c r="I20" s="14">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="J20" s="14">
-        <v>376</v>
+        <v>416</v>
       </c>
       <c r="K20" s="15">
-        <v>-4.521276595744</v>
+        <v>-6.971153846153</v>
       </c>
       <c r="L20" s="15">
-        <v>-9.798994974874</v>
+        <v>-9.790209790209</v>
       </c>
       <c r="M20" s="15">
-        <v>2.571428571428</v>
+        <v>-0.514138817480</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.380552220888</v>
+        <v>-91.566790150359</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C21" s="17">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="D21" s="17">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="E21" s="18">
-        <v>-1.913875598086</v>
+        <v>-5.911330049261</v>
       </c>
       <c r="F21" s="17">
-        <v>753</v>
+        <v>785</v>
       </c>
       <c r="G21" s="17">
-        <v>773</v>
+        <v>793</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.587322121604</v>
+        <v>-1.008827238335</v>
       </c>
       <c r="I21" s="17">
-        <v>2126</v>
+        <v>2318</v>
       </c>
       <c r="J21" s="17">
-        <v>2171</v>
+        <v>2375</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.072777521879</v>
+        <v>-2.4</v>
       </c>
       <c r="L21" s="18">
-        <v>-9.991532599491</v>
+        <v>-9.453125</v>
       </c>
       <c r="M21" s="18">
-        <v>-4.104645917907</v>
+        <v>-4.451772464962</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.416243654822</v>
+        <v>-78.539024164429</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>3</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="F22" s="14">
+        <v>6</v>
+      </c>
+      <c r="G22" s="14">
         <v>8</v>
       </c>
-      <c r="G22" s="14">
-        <v>6</v>
-      </c>
       <c r="H22" s="15">
-        <v>33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="I22" s="14">
         <v>33</v>
       </c>
       <c r="J22" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K22" s="15">
-        <v>135.714285714286</v>
+        <v>94.117647058823</v>
       </c>
       <c r="L22" s="15">
+        <v>-8.333333333333</v>
+      </c>
+      <c r="M22" s="15">
         <v>3.125</v>
       </c>
-      <c r="M22" s="15">
-        <v>10</v>
-      </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" s="14">
         <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-66.666666666666</v>
+        <v>200</v>
       </c>
       <c r="F23" s="14">
         <v>12</v>
       </c>
       <c r="G23" s="14">
+        <v>21</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-42.857142857142</v>
+      </c>
+      <c r="I23" s="14">
+        <v>36</v>
+      </c>
+      <c r="J23" s="14">
+        <v>56</v>
+      </c>
+      <c r="K23" s="15">
+        <v>-35.714285714285</v>
+      </c>
+      <c r="L23" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="M23" s="15">
+        <v>-20</v>
+      </c>
+      <c r="N23" s="13" t="s">
         <v>28</v>
-      </c>
-      <c r="H23" s="15">
-        <v>-57.142857142857</v>
-      </c>
-      <c r="I23" s="14">
-        <v>33</v>
-      </c>
-      <c r="J23" s="14">
-        <v>55</v>
-      </c>
-      <c r="K23" s="15">
-        <v>-40</v>
-      </c>
-      <c r="L23" s="15">
-        <v>-26.666666666666</v>
-      </c>
-      <c r="M23" s="15">
-        <v>-21.428571428571</v>
-      </c>
-      <c r="N23" s="13" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" s="14">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="D24" s="14">
-        <v>195</v>
+        <v>166</v>
       </c>
       <c r="E24" s="15">
-        <v>-25.641025641025</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>646</v>
+        <v>700</v>
       </c>
       <c r="G24" s="14">
-        <v>664</v>
+        <v>678</v>
       </c>
       <c r="H24" s="15">
-        <v>-2.710843373493</v>
+        <v>3.244837758112</v>
       </c>
       <c r="I24" s="14">
-        <v>1931</v>
+        <v>2098</v>
       </c>
       <c r="J24" s="14">
-        <v>1877</v>
+        <v>2044</v>
       </c>
       <c r="K24" s="15">
-        <v>2.876931273308</v>
+        <v>2.641878669275</v>
       </c>
       <c r="L24" s="15">
-        <v>-2.671370967741</v>
+        <v>-2.099860009332</v>
       </c>
       <c r="M24" s="15">
-        <v>61.319966583124</v>
+        <v>61.260568793236</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" s="14">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="D25" s="14">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E25" s="15">
-        <v>-32.954545454545</v>
+        <v>-5.194805194805</v>
       </c>
       <c r="F25" s="14">
-        <v>234</v>
+        <v>268</v>
       </c>
       <c r="G25" s="14">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="H25" s="15">
-        <v>-15.217391304347</v>
+        <v>-7.903780068728</v>
       </c>
       <c r="I25" s="14">
-        <v>729</v>
+        <v>802</v>
       </c>
       <c r="J25" s="14">
-        <v>767</v>
+        <v>844</v>
       </c>
       <c r="K25" s="15">
-        <v>-4.954367666232</v>
+        <v>-4.976303317535</v>
       </c>
       <c r="L25" s="15">
-        <v>-7.133757961783</v>
+        <v>-7.175925925925</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="14">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D26" s="14">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="E26" s="15">
-        <v>21.126760563380</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>376</v>
+        <v>401</v>
       </c>
       <c r="G26" s="14">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="H26" s="15">
-        <v>20.127795527156</v>
+        <v>23.384615384615</v>
       </c>
       <c r="I26" s="14">
-        <v>944</v>
+        <v>1035</v>
       </c>
       <c r="J26" s="14">
-        <v>948</v>
+        <v>1037</v>
       </c>
       <c r="K26" s="15">
-        <v>-0.421940928270</v>
+        <v>-0.192864030858</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.356636271529</v>
+        <v>-2.266288951841</v>
       </c>
       <c r="M26" s="15">
-        <v>-2.176165803108</v>
+        <v>-0.480769230769</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D27" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>-42.857142857142</v>
+        <v>400</v>
       </c>
       <c r="F27" s="14">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G27" s="14">
         <v>19</v>
       </c>
       <c r="H27" s="15">
-        <v>15.789473684210</v>
+        <v>57.894736842105</v>
       </c>
       <c r="I27" s="14">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="J27" s="14">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K27" s="15">
-        <v>11.111111111111</v>
+        <v>26.785714285714</v>
       </c>
       <c r="L27" s="15">
-        <v>1.694915254237</v>
+        <v>9.230769230769</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" s="14">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D28" s="14">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E28" s="15">
-        <v>6.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F28" s="14">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G28" s="14">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H28" s="15">
-        <v>30.769230769230</v>
+        <v>60.606060606060</v>
       </c>
       <c r="I28" s="14">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="J28" s="14">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="K28" s="15">
-        <v>8.737864077669</v>
+        <v>8.108108108108</v>
       </c>
       <c r="L28" s="15">
-        <v>31.764705882352</v>
+        <v>36.363636363636</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0</v>
       </c>
       <c r="F29" s="14">
         <v>3</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I29" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J29" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K29" s="15">
-        <v>-52.941176470588</v>
+        <v>-50</v>
       </c>
       <c r="L29" s="15">
-        <v>-61.904761904761</v>
+        <v>-60.869565217391</v>
       </c>
       <c r="M29" s="15">
-        <v>-80.487804878048</v>
+        <v>-79.545454545454</v>
       </c>
       <c r="N29" s="15">
-        <v>-92.792792792792</v>
+        <v>-92.682926829268</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
       </c>
       <c r="F30" s="14">
         <v>3</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I30" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J30" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K30" s="15">
         <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-57.894736842105</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M30" s="15">
-        <v>-75</v>
+        <v>-73.529411764705</v>
       </c>
       <c r="N30" s="15">
-        <v>-92</v>
+        <v>-91.818181818181</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>4</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>200</v>
       </c>
       <c r="I31" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J31" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K31" s="15">
-        <v>83.333333333333</v>
+        <v>71.428571428571</v>
       </c>
       <c r="L31" s="15">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1608,40 +1608,40 @@
         <v>40</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>38</v>
+      </c>
+      <c r="D33" s="14">
+        <v>2</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="14">
         <v>3</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="14">
+        <v>2</v>
+      </c>
+      <c r="H33" s="15">
+        <v>50</v>
       </c>
       <c r="I33" s="14">
         <v>4</v>
       </c>
       <c r="J33" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K33" s="15">
-        <v>-20</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L33" s="15">
         <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C40" s="14">
         <v>341</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C41" s="14">
         <v>8056</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C42" s="14">
         <v>3941</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C43" s="14">
         <v>11976</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C44" s="14">
         <v>7856</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C45" s="14">
         <v>21758</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C46" s="17">
         <v>54089</v>

--- a/data/source/weekly/cs-en-us-pbqs.xlsx
+++ b/data/source/weekly/cs-en-us-pbqs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -199,6 +199,12 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -223,9 +229,6 @@
     <t>Transit</t>
   </si>
   <si>
-    <t>***.*</t>
-  </si>
-  <si>
     <t>Housing</t>
   </si>
   <si>
@@ -251,9 +254,6 @@
   </si>
   <si>
     <t>Hate Crimes</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>Traffic Statistics</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -851,14 +851,14 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
-      </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>0</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
         <v>2</v>
@@ -879,18 +879,18 @@
         <v>-18.181818181818</v>
       </c>
       <c r="L14" s="15">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="M14" s="15">
-        <v>-35.714285714285</v>
+        <v>-43.75</v>
       </c>
       <c r="N14" s="15">
-        <v>-77.5</v>
+        <v>-78.048780487804</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
         <v>6</v>
@@ -902,687 +902,687 @@
         <v>200</v>
       </c>
       <c r="F15" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G15" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H15" s="15">
-        <v>37.5</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I15" s="14">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J15" s="14">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K15" s="15">
-        <v>11.111111111111</v>
+        <v>19.148936170212</v>
       </c>
       <c r="L15" s="15">
-        <v>21.951219512195</v>
+        <v>24.444444444444</v>
       </c>
       <c r="M15" s="15">
-        <v>85.185185185185</v>
+        <v>93.103448275862</v>
       </c>
       <c r="N15" s="15">
-        <v>-38.271604938271</v>
+        <v>-37.078651685393</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D16" s="14">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E16" s="15">
-        <v>-4.761904761904</v>
+        <v>92.307692307692</v>
       </c>
       <c r="F16" s="14">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G16" s="14">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H16" s="15">
-        <v>-1.234567901234</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I16" s="14">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="J16" s="14">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="K16" s="15">
-        <v>-0.390625</v>
+        <v>4.460966542750</v>
       </c>
       <c r="L16" s="15">
-        <v>-16.393442622950</v>
+        <v>-13.538461538461</v>
       </c>
       <c r="M16" s="15">
-        <v>-51.886792452830</v>
+        <v>-49.369369369369</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.319742489270</v>
+        <v>-85.921843687374</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>63</v>
+      </c>
+      <c r="D17" s="14">
         <v>53</v>
       </c>
-      <c r="D17" s="14">
-        <v>40</v>
-      </c>
       <c r="E17" s="15">
-        <v>32.5</v>
+        <v>18.867924528301</v>
       </c>
       <c r="F17" s="14">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="G17" s="14">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="H17" s="15">
-        <v>0.476190476190</v>
+        <v>15.048543689320</v>
       </c>
       <c r="I17" s="14">
-        <v>661</v>
+        <v>728</v>
       </c>
       <c r="J17" s="14">
-        <v>661</v>
+        <v>714</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>1.960784313725</v>
       </c>
       <c r="L17" s="15">
-        <v>-7.032348804500</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="M17" s="15">
-        <v>80.601092896174</v>
+        <v>83.375314861461</v>
       </c>
       <c r="N17" s="15">
-        <v>-17.167919799498</v>
+        <v>-14.654161781946</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="14">
+        <v>12</v>
+      </c>
+      <c r="D18" s="14">
         <v>23</v>
       </c>
-      <c r="C18" s="14">
-        <v>21</v>
-      </c>
-      <c r="D18" s="14">
-        <v>30</v>
-      </c>
       <c r="E18" s="15">
-        <v>-30</v>
+        <v>-47.826086956521</v>
       </c>
       <c r="F18" s="14">
         <v>60</v>
       </c>
       <c r="G18" s="14">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="H18" s="15">
-        <v>-40.594059405940</v>
+        <v>-44.954128440367</v>
       </c>
       <c r="I18" s="14">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="J18" s="14">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="K18" s="15">
-        <v>-35.205992509363</v>
+        <v>-35.172413793103</v>
       </c>
       <c r="L18" s="15">
-        <v>-27.004219409282</v>
+        <v>-28.787878787878</v>
       </c>
       <c r="M18" s="15">
-        <v>-62.309368191721</v>
+        <v>-62.020202020202</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.742243436754</v>
+        <v>-91.718061674008</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D19" s="14">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E19" s="15">
-        <v>-11.594202898550</v>
+        <v>29.629629629629</v>
       </c>
       <c r="F19" s="14">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G19" s="14">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="H19" s="15">
-        <v>14.406779661016</v>
+        <v>17.105263157894</v>
       </c>
       <c r="I19" s="14">
-        <v>783</v>
+        <v>856</v>
       </c>
       <c r="J19" s="14">
-        <v>719</v>
+        <v>773</v>
       </c>
       <c r="K19" s="15">
-        <v>8.901251738525</v>
+        <v>10.737386804657</v>
       </c>
       <c r="L19" s="15">
-        <v>-5.434782608695</v>
+        <v>-4.143337066069</v>
       </c>
       <c r="M19" s="15">
-        <v>22.152886115444</v>
+        <v>23.342939481268</v>
       </c>
       <c r="N19" s="15">
-        <v>-41.304347826087</v>
+        <v>-44.631306597671</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D20" s="14">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E20" s="15">
-        <v>-27.5</v>
+        <v>41.935483870967</v>
       </c>
       <c r="F20" s="14">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="G20" s="14">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H20" s="15">
-        <v>-5.405405405405</v>
+        <v>-4.575163398692</v>
       </c>
       <c r="I20" s="14">
-        <v>387</v>
+        <v>428</v>
       </c>
       <c r="J20" s="14">
-        <v>416</v>
+        <v>447</v>
       </c>
       <c r="K20" s="15">
-        <v>-6.971153846153</v>
+        <v>-4.250559284116</v>
       </c>
       <c r="L20" s="15">
-        <v>-9.790209790209</v>
+        <v>-8.351177730192</v>
       </c>
       <c r="M20" s="15">
-        <v>-0.514138817480</v>
+        <v>0.705882352941</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.566790150359</v>
+        <v>-91.422845691382</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="D21" s="17">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="E21" s="18">
-        <v>-5.911330049261</v>
+        <v>25</v>
       </c>
       <c r="F21" s="17">
-        <v>785</v>
+        <v>816</v>
       </c>
       <c r="G21" s="17">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="H21" s="18">
-        <v>-1.008827238335</v>
+        <v>3.684879288437</v>
       </c>
       <c r="I21" s="17">
-        <v>2318</v>
+        <v>2546</v>
       </c>
       <c r="J21" s="17">
-        <v>2375</v>
+        <v>2551</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.4</v>
+        <v>-0.196001568012</v>
       </c>
       <c r="L21" s="18">
-        <v>-9.453125</v>
+        <v>-7.686729514140</v>
       </c>
       <c r="M21" s="18">
-        <v>-4.451772464962</v>
+        <v>-2.489467636920</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.539024164429</v>
+        <v>-78.396266440390</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C22" s="14">
+        <v>6</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="14">
-        <v>3</v>
-      </c>
       <c r="E22" s="15">
-        <v>-66.666666666666</v>
+        <v>500</v>
       </c>
       <c r="F22" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G22" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>-25</v>
+        <v>60</v>
       </c>
       <c r="I22" s="14">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J22" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K22" s="15">
-        <v>94.117647058823</v>
+        <v>116.666666666667</v>
       </c>
       <c r="L22" s="15">
-        <v>-8.333333333333</v>
+        <v>5.405405405405</v>
       </c>
       <c r="M22" s="15">
-        <v>3.125</v>
+        <v>21.875</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>2</v>
+      </c>
+      <c r="D23" s="14">
         <v>3</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
       <c r="E23" s="15">
-        <v>200</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F23" s="14">
         <v>12</v>
       </c>
       <c r="G23" s="14">
+        <v>16</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-25</v>
+      </c>
+      <c r="I23" s="14">
+        <v>39</v>
+      </c>
+      <c r="J23" s="14">
+        <v>59</v>
+      </c>
+      <c r="K23" s="15">
+        <v>-33.898305084745</v>
+      </c>
+      <c r="L23" s="15">
+        <v>-31.578947368421</v>
+      </c>
+      <c r="M23" s="15">
+        <v>-17.021276595744</v>
+      </c>
+      <c r="N23" s="13" t="s">
         <v>21</v>
-      </c>
-      <c r="H23" s="15">
-        <v>-42.857142857142</v>
-      </c>
-      <c r="I23" s="14">
-        <v>36</v>
-      </c>
-      <c r="J23" s="14">
-        <v>56</v>
-      </c>
-      <c r="K23" s="15">
-        <v>-35.714285714285</v>
-      </c>
-      <c r="L23" s="15">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="M23" s="15">
-        <v>-20</v>
-      </c>
-      <c r="N23" s="13" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>166</v>
+        <v>229</v>
       </c>
       <c r="D24" s="14">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>38.787878787878</v>
       </c>
       <c r="F24" s="14">
-        <v>700</v>
+        <v>725</v>
       </c>
       <c r="G24" s="14">
-        <v>678</v>
+        <v>701</v>
       </c>
       <c r="H24" s="15">
-        <v>3.244837758112</v>
+        <v>3.423680456490</v>
       </c>
       <c r="I24" s="14">
-        <v>2098</v>
+        <v>2326</v>
       </c>
       <c r="J24" s="14">
-        <v>2044</v>
+        <v>2209</v>
       </c>
       <c r="K24" s="15">
-        <v>2.641878669275</v>
+        <v>5.296514259846</v>
       </c>
       <c r="L24" s="15">
-        <v>-2.099860009332</v>
+        <v>0.129143349117</v>
       </c>
       <c r="M24" s="15">
-        <v>61.260568793236</v>
+        <v>63.457484188334</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="D25" s="14">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="E25" s="15">
-        <v>-5.194805194805</v>
+        <v>37.5</v>
       </c>
       <c r="F25" s="14">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="G25" s="14">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="H25" s="15">
-        <v>-7.903780068728</v>
+        <v>-7.371794871794</v>
       </c>
       <c r="I25" s="14">
-        <v>802</v>
+        <v>893</v>
       </c>
       <c r="J25" s="14">
-        <v>844</v>
+        <v>908</v>
       </c>
       <c r="K25" s="15">
-        <v>-4.976303317535</v>
+        <v>-1.651982378854</v>
       </c>
       <c r="L25" s="15">
-        <v>-7.175925925925</v>
+        <v>-4.898828541001</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="D26" s="14">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E26" s="15">
-        <v>-3.333333333333</v>
+        <v>10.752688172043</v>
       </c>
       <c r="F26" s="14">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="G26" s="14">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H26" s="15">
-        <v>23.384615384615</v>
+        <v>22.839506172839</v>
       </c>
       <c r="I26" s="14">
-        <v>1035</v>
+        <v>1135</v>
       </c>
       <c r="J26" s="14">
-        <v>1037</v>
+        <v>1130</v>
       </c>
       <c r="K26" s="15">
-        <v>-0.192864030858</v>
+        <v>0.442477876106</v>
       </c>
       <c r="L26" s="15">
-        <v>-2.266288951841</v>
+        <v>-0.351185250219</v>
       </c>
       <c r="M26" s="15">
-        <v>-0.480769230769</v>
+        <v>1.611459265890</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>7</v>
+      </c>
+      <c r="D27" s="14">
+        <v>5</v>
+      </c>
+      <c r="E27" s="15">
+        <v>40</v>
+      </c>
+      <c r="F27" s="14">
+        <v>28</v>
+      </c>
+      <c r="G27" s="14">
+        <v>17</v>
+      </c>
+      <c r="H27" s="15">
+        <v>64.705882352941</v>
+      </c>
+      <c r="I27" s="14">
+        <v>77</v>
+      </c>
+      <c r="J27" s="14">
+        <v>61</v>
+      </c>
+      <c r="K27" s="15">
+        <v>26.229508196721</v>
+      </c>
+      <c r="L27" s="15">
         <v>10</v>
       </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>400</v>
-      </c>
-      <c r="F27" s="14">
-        <v>30</v>
-      </c>
-      <c r="G27" s="14">
-        <v>19</v>
-      </c>
-      <c r="H27" s="15">
-        <v>57.894736842105</v>
-      </c>
-      <c r="I27" s="14">
-        <v>71</v>
-      </c>
-      <c r="J27" s="14">
-        <v>56</v>
-      </c>
-      <c r="K27" s="15">
-        <v>26.785714285714</v>
-      </c>
-      <c r="L27" s="15">
-        <v>9.230769230769</v>
-      </c>
       <c r="M27" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>7</v>
+      </c>
+      <c r="D28" s="14">
         <v>8</v>
       </c>
-      <c r="D28" s="14">
-        <v>7</v>
-      </c>
       <c r="E28" s="15">
-        <v>14.285714285714</v>
+        <v>-12.5</v>
       </c>
       <c r="F28" s="14">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G28" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H28" s="15">
-        <v>60.606060606060</v>
+        <v>21.052631578947</v>
       </c>
       <c r="I28" s="14">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="J28" s="14">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="K28" s="15">
-        <v>8.108108108108</v>
+        <v>8.403361344537</v>
       </c>
       <c r="L28" s="15">
-        <v>36.363636363636</v>
+        <v>35.789473684210</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>1</v>
-      </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G29" s="14">
         <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="I29" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J29" s="14">
         <v>18</v>
       </c>
       <c r="K29" s="15">
-        <v>-50</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="L29" s="15">
-        <v>-60.869565217391</v>
+        <v>-54.166666666666</v>
       </c>
       <c r="M29" s="15">
-        <v>-79.545454545454</v>
+        <v>-78</v>
       </c>
       <c r="N29" s="15">
-        <v>-92.682926829268</v>
+        <v>-91.729323308270</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>1</v>
-      </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G30" s="14">
         <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="I30" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J30" s="14">
         <v>9</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L30" s="15">
-        <v>-57.142857142857</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-73.529411764705</v>
+        <v>-72.5</v>
       </c>
       <c r="N30" s="15">
-        <v>-91.818181818181</v>
+        <v>-90.756302521008</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+        <v>20</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I31" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J31" s="14">
         <v>7</v>
       </c>
       <c r="K31" s="15">
-        <v>71.428571428571</v>
+        <v>85.714285714285</v>
       </c>
       <c r="L31" s="15">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1608,13 +1608,13 @@
         <v>40</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D33" s="14">
-        <v>2</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+        <v>20</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="14">
         <v>3</v>
@@ -1635,13 +1635,13 @@
         <v>-42.857142857142</v>
       </c>
       <c r="L33" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>341</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>8056</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>3941</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>11976</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>7856</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>21758</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>54089</v>

--- a/data/source/weekly/cs-en-us-pbqs.xlsx
+++ b/data/source/weekly/cs-en-us-pbqs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>2</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -861,31 +861,31 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="14">
         <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I14" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J14" s="14">
         <v>11</v>
       </c>
       <c r="K14" s="15">
-        <v>-18.181818181818</v>
+        <v>0</v>
       </c>
       <c r="L14" s="15">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="M14" s="15">
-        <v>-43.75</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="N14" s="15">
-        <v>-78.048780487804</v>
+        <v>-74.418604651162</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -896,37 +896,37 @@
         <v>6</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F15" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G15" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H15" s="15">
-        <v>66.666666666666</v>
+        <v>61.538461538461</v>
       </c>
       <c r="I15" s="14">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="J15" s="14">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K15" s="15">
-        <v>19.148936170212</v>
+        <v>24</v>
       </c>
       <c r="L15" s="15">
-        <v>24.444444444444</v>
+        <v>26.530612244898</v>
       </c>
       <c r="M15" s="15">
-        <v>93.103448275862</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>-37.078651685393</v>
+        <v>-32.608695652173</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D16" s="14">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E16" s="15">
-        <v>92.307692307692</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="F16" s="14">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G16" s="14">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H16" s="15">
-        <v>7.692307692307</v>
+        <v>1.149425287356</v>
       </c>
       <c r="I16" s="14">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="J16" s="14">
-        <v>269</v>
+        <v>295</v>
       </c>
       <c r="K16" s="15">
-        <v>4.460966542750</v>
+        <v>2.711864406779</v>
       </c>
       <c r="L16" s="15">
-        <v>-13.538461538461</v>
+        <v>-13.428571428571</v>
       </c>
       <c r="M16" s="15">
-        <v>-49.369369369369</v>
+        <v>-48.644067796610</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.921843687374</v>
+        <v>-85.700802265219</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D17" s="14">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E17" s="15">
-        <v>18.867924528301</v>
+        <v>5.172413793103</v>
       </c>
       <c r="F17" s="14">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G17" s="14">
         <v>206</v>
       </c>
       <c r="H17" s="15">
-        <v>15.048543689320</v>
+        <v>19.417475728155</v>
       </c>
       <c r="I17" s="14">
-        <v>728</v>
+        <v>797</v>
       </c>
       <c r="J17" s="14">
-        <v>714</v>
+        <v>772</v>
       </c>
       <c r="K17" s="15">
-        <v>1.960784313725</v>
+        <v>3.238341968911</v>
       </c>
       <c r="L17" s="15">
-        <v>-3.448275862068</v>
+        <v>-2.447980416156</v>
       </c>
       <c r="M17" s="15">
-        <v>83.375314861461</v>
+        <v>88.862559241706</v>
       </c>
       <c r="N17" s="15">
-        <v>-14.654161781946</v>
+        <v>-12.800875273523</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D18" s="14">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E18" s="15">
-        <v>-47.826086956521</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="G18" s="14">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="H18" s="15">
-        <v>-44.954128440367</v>
+        <v>-21.276595744680</v>
       </c>
       <c r="I18" s="14">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="J18" s="14">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="K18" s="15">
-        <v>-35.172413793103</v>
+        <v>-31.493506493506</v>
       </c>
       <c r="L18" s="15">
-        <v>-28.787878787878</v>
+        <v>-25.704225352112</v>
       </c>
       <c r="M18" s="15">
-        <v>-62.020202020202</v>
+        <v>-60.188679245283</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.718061674008</v>
+        <v>-91.324013157894</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D19" s="14">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E19" s="15">
-        <v>29.629629629629</v>
+        <v>62.264150943396</v>
       </c>
       <c r="F19" s="14">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="G19" s="14">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H19" s="15">
-        <v>17.105263157894</v>
+        <v>22.566371681415</v>
       </c>
       <c r="I19" s="14">
-        <v>856</v>
+        <v>940</v>
       </c>
       <c r="J19" s="14">
-        <v>773</v>
+        <v>826</v>
       </c>
       <c r="K19" s="15">
-        <v>10.737386804657</v>
+        <v>13.801452784503</v>
       </c>
       <c r="L19" s="15">
-        <v>-4.143337066069</v>
+        <v>-1.467505241090</v>
       </c>
       <c r="M19" s="15">
-        <v>23.342939481268</v>
+        <v>26.174496644295</v>
       </c>
       <c r="N19" s="15">
-        <v>-44.631306597671</v>
+        <v>-46.832579185520</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D20" s="14">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E20" s="15">
-        <v>41.935483870967</v>
+        <v>-35</v>
       </c>
       <c r="F20" s="14">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="G20" s="14">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H20" s="15">
-        <v>-4.575163398692</v>
+        <v>-13.75</v>
       </c>
       <c r="I20" s="14">
-        <v>428</v>
+        <v>453</v>
       </c>
       <c r="J20" s="14">
-        <v>447</v>
+        <v>487</v>
       </c>
       <c r="K20" s="15">
-        <v>-4.250559284116</v>
+        <v>-6.981519507186</v>
       </c>
       <c r="L20" s="15">
-        <v>-8.351177730192</v>
+        <v>-8.853118712273</v>
       </c>
       <c r="M20" s="15">
-        <v>0.705882352941</v>
+        <v>-0.657894736842</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.422845691382</v>
+        <v>-91.539036234591</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D21" s="17">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="E21" s="18">
-        <v>25</v>
+        <v>13.636363636363</v>
       </c>
       <c r="F21" s="17">
-        <v>816</v>
+        <v>847</v>
       </c>
       <c r="G21" s="17">
         <v>787</v>
       </c>
       <c r="H21" s="18">
-        <v>3.684879288437</v>
+        <v>7.623888182973</v>
       </c>
       <c r="I21" s="17">
-        <v>2546</v>
+        <v>2777</v>
       </c>
       <c r="J21" s="17">
-        <v>2551</v>
+        <v>2749</v>
       </c>
       <c r="K21" s="18">
-        <v>-0.196001568012</v>
+        <v>1.018552200800</v>
       </c>
       <c r="L21" s="18">
-        <v>-7.686729514140</v>
+        <v>-6.214116852414</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.489467636920</v>
+        <v>-0.501612325331</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.396266440390</v>
+        <v>-78.171671120892</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,13 +1180,13 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F22" s="14">
         <v>8</v>
@@ -1201,16 +1201,16 @@
         <v>39</v>
       </c>
       <c r="J22" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K22" s="15">
-        <v>116.666666666667</v>
+        <v>105.263157894737</v>
       </c>
       <c r="L22" s="15">
         <v>5.405405405405</v>
       </c>
       <c r="M22" s="15">
-        <v>21.875</v>
+        <v>11.428571428571</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-33.333333333333</v>
+        <v>900</v>
       </c>
       <c r="F23" s="14">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G23" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H23" s="15">
-        <v>-25</v>
+        <v>35.714285714285</v>
       </c>
       <c r="I23" s="14">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="J23" s="14">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K23" s="15">
-        <v>-33.898305084745</v>
+        <v>-15</v>
       </c>
       <c r="L23" s="15">
-        <v>-31.578947368421</v>
+        <v>-13.559322033898</v>
       </c>
       <c r="M23" s="15">
-        <v>-17.021276595744</v>
+        <v>6.25</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>229</v>
+        <v>164</v>
       </c>
       <c r="D24" s="14">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="E24" s="15">
-        <v>38.787878787878</v>
+        <v>25.190839694656</v>
       </c>
       <c r="F24" s="14">
-        <v>725</v>
+        <v>703</v>
       </c>
       <c r="G24" s="14">
-        <v>701</v>
+        <v>658</v>
       </c>
       <c r="H24" s="15">
-        <v>3.423680456490</v>
+        <v>6.838905775075</v>
       </c>
       <c r="I24" s="14">
-        <v>2326</v>
+        <v>2486</v>
       </c>
       <c r="J24" s="14">
-        <v>2209</v>
+        <v>2340</v>
       </c>
       <c r="K24" s="15">
-        <v>5.296514259846</v>
+        <v>6.239316239316</v>
       </c>
       <c r="L24" s="15">
-        <v>0.129143349117</v>
+        <v>-0.798084596967</v>
       </c>
       <c r="M24" s="15">
-        <v>63.457484188334</v>
+        <v>61.114711600777</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="D25" s="14">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="E25" s="15">
-        <v>37.5</v>
+        <v>-20</v>
       </c>
       <c r="F25" s="14">
-        <v>289</v>
+        <v>268</v>
       </c>
       <c r="G25" s="14">
-        <v>312</v>
+        <v>284</v>
       </c>
       <c r="H25" s="15">
-        <v>-7.371794871794</v>
+        <v>-5.633802816901</v>
       </c>
       <c r="I25" s="14">
-        <v>893</v>
+        <v>938</v>
       </c>
       <c r="J25" s="14">
-        <v>908</v>
+        <v>963</v>
       </c>
       <c r="K25" s="15">
-        <v>-1.651982378854</v>
+        <v>-2.596053997923</v>
       </c>
       <c r="L25" s="15">
-        <v>-4.898828541001</v>
+        <v>-7.220573689416</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="D26" s="14">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E26" s="15">
-        <v>10.752688172043</v>
+        <v>3.448275862068</v>
       </c>
       <c r="F26" s="14">
-        <v>398</v>
+        <v>370</v>
       </c>
       <c r="G26" s="14">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="H26" s="15">
-        <v>22.839506172839</v>
+        <v>8.823529411764</v>
       </c>
       <c r="I26" s="14">
-        <v>1135</v>
+        <v>1224</v>
       </c>
       <c r="J26" s="14">
-        <v>1130</v>
+        <v>1217</v>
       </c>
       <c r="K26" s="15">
-        <v>0.442477876106</v>
+        <v>0.575184880854</v>
       </c>
       <c r="L26" s="15">
-        <v>-0.351185250219</v>
+        <v>0</v>
       </c>
       <c r="M26" s="15">
-        <v>1.611459265890</v>
+        <v>1.661129568106</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,31 +1388,31 @@
         <v>7</v>
       </c>
       <c r="D27" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E27" s="15">
-        <v>40</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F27" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G27" s="14">
         <v>17</v>
       </c>
       <c r="H27" s="15">
-        <v>64.705882352941</v>
+        <v>70.588235294117</v>
       </c>
       <c r="I27" s="14">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J27" s="14">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K27" s="15">
-        <v>26.229508196721</v>
+        <v>31.25</v>
       </c>
       <c r="L27" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1435,25 +1435,25 @@
         <v>-12.5</v>
       </c>
       <c r="F28" s="14">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G28" s="14">
         <v>38</v>
       </c>
       <c r="H28" s="15">
-        <v>21.052631578947</v>
+        <v>10.526315789473</v>
       </c>
       <c r="I28" s="14">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="J28" s="14">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="K28" s="15">
-        <v>8.403361344537</v>
+        <v>8.661417322834</v>
       </c>
       <c r="L28" s="15">
-        <v>35.789473684210</v>
+        <v>33.980582524271</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1467,7 +1467,7 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1479,28 +1479,28 @@
         <v>5</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="I29" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J29" s="14">
         <v>18</v>
       </c>
       <c r="K29" s="15">
-        <v>-38.888888888888</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L29" s="15">
-        <v>-54.166666666666</v>
+        <v>-52</v>
       </c>
       <c r="M29" s="15">
-        <v>-78</v>
+        <v>-77.358490566037</v>
       </c>
       <c r="N29" s="15">
-        <v>-91.729323308270</v>
+        <v>-91.489361702127</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,7 +1508,7 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1520,28 +1520,28 @@
         <v>5</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="I30" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J30" s="14">
         <v>9</v>
       </c>
       <c r="K30" s="15">
-        <v>22.222222222222</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-47.826086956521</v>
       </c>
       <c r="M30" s="15">
-        <v>-72.5</v>
+        <v>-72.093023255813</v>
       </c>
       <c r="N30" s="15">
-        <v>-90.756302521008</v>
+        <v>-90.476190476190</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1558,13 +1558,13 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I31" s="14">
         <v>13</v>
@@ -1576,7 +1576,7 @@
         <v>85.714285714285</v>
       </c>
       <c r="L31" s="15">
-        <v>62.5</v>
+        <v>44.444444444444</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1616,14 +1616,14 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="14">
-        <v>3</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="14">
         <v>2</v>
       </c>
       <c r="H33" s="15">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="I33" s="14">
         <v>4</v>

--- a/data/source/weekly/cs-en-us-pbqs.xlsx
+++ b/data/source/weekly/cs-en-us-pbqs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -852,7 +852,7 @@
         <v>19</v>
       </c>
       <c r="C14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -861,31 +861,31 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14" s="14">
         <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I14" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J14" s="14">
         <v>11</v>
       </c>
       <c r="K14" s="15">
-        <v>0</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L14" s="15">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M14" s="15">
-        <v>-35.294117647058</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="N14" s="15">
-        <v>-74.418604651162</v>
+        <v>-75.510204081632</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F15" s="14">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G15" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H15" s="15">
-        <v>61.538461538461</v>
+        <v>181.818181818182</v>
       </c>
       <c r="I15" s="14">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="J15" s="14">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K15" s="15">
-        <v>24</v>
+        <v>37.037037037037</v>
       </c>
       <c r="L15" s="15">
-        <v>26.530612244898</v>
+        <v>39.622641509434</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>111.428571428571</v>
       </c>
       <c r="N15" s="15">
-        <v>-32.608695652173</v>
+        <v>-26.732673267326</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E16" s="15">
-        <v>-11.538461538461</v>
+        <v>17.647058823529</v>
       </c>
       <c r="F16" s="14">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G16" s="14">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H16" s="15">
-        <v>1.149425287356</v>
+        <v>16.883116883116</v>
       </c>
       <c r="I16" s="14">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="J16" s="14">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="K16" s="15">
-        <v>2.711864406779</v>
+        <v>4.166666666666</v>
       </c>
       <c r="L16" s="15">
-        <v>-13.428571428571</v>
+        <v>-12.868632707774</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.644067796610</v>
+        <v>-47.154471544715</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.700802265219</v>
+        <v>-85.471613768439</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D17" s="14">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="E17" s="15">
-        <v>5.172413793103</v>
+        <v>39.024390243902</v>
       </c>
       <c r="F17" s="14">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="G17" s="14">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="H17" s="15">
-        <v>19.417475728155</v>
+        <v>25</v>
       </c>
       <c r="I17" s="14">
-        <v>797</v>
+        <v>856</v>
       </c>
       <c r="J17" s="14">
-        <v>772</v>
+        <v>813</v>
       </c>
       <c r="K17" s="15">
-        <v>3.238341968911</v>
+        <v>5.289052890528</v>
       </c>
       <c r="L17" s="15">
-        <v>-2.447980416156</v>
+        <v>-2.947845804988</v>
       </c>
       <c r="M17" s="15">
-        <v>88.862559241706</v>
+        <v>86.899563318777</v>
       </c>
       <c r="N17" s="15">
-        <v>-12.800875273523</v>
+        <v>-11.387163561076</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E18" s="15">
-        <v>16.666666666666</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G18" s="14">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H18" s="15">
-        <v>-21.276595744680</v>
+        <v>-6.024096385542</v>
       </c>
       <c r="I18" s="14">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="J18" s="14">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="K18" s="15">
-        <v>-31.493506493506</v>
+        <v>-27.8125</v>
       </c>
       <c r="L18" s="15">
-        <v>-25.704225352112</v>
+        <v>-23.255813953488</v>
       </c>
       <c r="M18" s="15">
-        <v>-60.188679245283</v>
+        <v>-58.896797153024</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.324013157894</v>
+        <v>-91.142638036809</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D19" s="14">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E19" s="15">
-        <v>62.264150943396</v>
+        <v>35.593220338983</v>
       </c>
       <c r="F19" s="14">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="G19" s="14">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="H19" s="15">
-        <v>22.566371681415</v>
+        <v>23.829787234042</v>
       </c>
       <c r="I19" s="14">
-        <v>940</v>
+        <v>1024</v>
       </c>
       <c r="J19" s="14">
-        <v>826</v>
+        <v>885</v>
       </c>
       <c r="K19" s="15">
-        <v>13.801452784503</v>
+        <v>15.706214689265</v>
       </c>
       <c r="L19" s="15">
-        <v>-1.467505241090</v>
+        <v>0.886699507389</v>
       </c>
       <c r="M19" s="15">
-        <v>26.174496644295</v>
+        <v>27.680798004987</v>
       </c>
       <c r="N19" s="15">
-        <v>-46.832579185520</v>
+        <v>-47.808358817533</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D20" s="14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E20" s="15">
-        <v>-35</v>
+        <v>-26.190476190476</v>
       </c>
       <c r="F20" s="14">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G20" s="14">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="H20" s="15">
-        <v>-13.75</v>
+        <v>-16.993464052287</v>
       </c>
       <c r="I20" s="14">
-        <v>453</v>
+        <v>484</v>
       </c>
       <c r="J20" s="14">
-        <v>487</v>
+        <v>529</v>
       </c>
       <c r="K20" s="15">
-        <v>-6.981519507186</v>
+        <v>-8.506616257088</v>
       </c>
       <c r="L20" s="15">
-        <v>-8.853118712273</v>
+        <v>-10.865561694291</v>
       </c>
       <c r="M20" s="15">
-        <v>-0.657894736842</v>
+        <v>0.414937759336</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.539036234591</v>
+        <v>-91.551754232850</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D21" s="17">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="E21" s="18">
-        <v>13.636363636363</v>
+        <v>25.142857142857</v>
       </c>
       <c r="F21" s="17">
-        <v>847</v>
+        <v>861</v>
       </c>
       <c r="G21" s="17">
-        <v>787</v>
+        <v>752</v>
       </c>
       <c r="H21" s="18">
-        <v>7.623888182973</v>
+        <v>14.494680851063</v>
       </c>
       <c r="I21" s="17">
-        <v>2777</v>
+        <v>3006</v>
       </c>
       <c r="J21" s="17">
-        <v>2749</v>
+        <v>2924</v>
       </c>
       <c r="K21" s="18">
-        <v>1.018552200800</v>
+        <v>2.804377564979</v>
       </c>
       <c r="L21" s="18">
-        <v>-6.214116852414</v>
+        <v>-5.382436260623</v>
       </c>
       <c r="M21" s="18">
-        <v>-0.501612325331</v>
+        <v>1.109989909182</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.171671120892</v>
+        <v>-77.981248168766</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="F22" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G22" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H22" s="15">
-        <v>60</v>
+        <v>57.142857142857</v>
       </c>
       <c r="I22" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J22" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K22" s="15">
-        <v>105.263157894737</v>
+        <v>104.761904761905</v>
       </c>
       <c r="L22" s="15">
-        <v>5.405405405405</v>
+        <v>7.5</v>
       </c>
       <c r="M22" s="15">
-        <v>11.428571428571</v>
+        <v>19.444444444444</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>900</v>
+        <v>50</v>
       </c>
       <c r="F23" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G23" s="14">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H23" s="15">
-        <v>35.714285714285</v>
+        <v>157.142857142857</v>
       </c>
       <c r="I23" s="14">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J23" s="14">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K23" s="15">
-        <v>-15</v>
+        <v>-14.516129032258</v>
       </c>
       <c r="L23" s="15">
-        <v>-13.559322033898</v>
+        <v>-14.516129032258</v>
       </c>
       <c r="M23" s="15">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D24" s="14">
-        <v>131</v>
+        <v>196</v>
       </c>
       <c r="E24" s="15">
-        <v>25.190839694656</v>
+        <v>-9.183673469387</v>
       </c>
       <c r="F24" s="14">
-        <v>703</v>
+        <v>741</v>
       </c>
       <c r="G24" s="14">
         <v>658</v>
       </c>
       <c r="H24" s="15">
-        <v>6.838905775075</v>
+        <v>12.613981762917</v>
       </c>
       <c r="I24" s="14">
-        <v>2486</v>
+        <v>2666</v>
       </c>
       <c r="J24" s="14">
-        <v>2340</v>
+        <v>2536</v>
       </c>
       <c r="K24" s="15">
-        <v>6.239316239316</v>
+        <v>5.126182965299</v>
       </c>
       <c r="L24" s="15">
-        <v>-0.798084596967</v>
+        <v>-1.623616236162</v>
       </c>
       <c r="M24" s="15">
-        <v>61.114711600777</v>
+        <v>59.069212410501</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="D25" s="14">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="E25" s="15">
-        <v>-20</v>
+        <v>-31.313131313131</v>
       </c>
       <c r="F25" s="14">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="G25" s="14">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="H25" s="15">
-        <v>-5.633802816901</v>
+        <v>-6.101694915254</v>
       </c>
       <c r="I25" s="14">
-        <v>938</v>
+        <v>1006</v>
       </c>
       <c r="J25" s="14">
-        <v>963</v>
+        <v>1062</v>
       </c>
       <c r="K25" s="15">
-        <v>-2.596053997923</v>
+        <v>-5.273069679849</v>
       </c>
       <c r="L25" s="15">
-        <v>-7.220573689416</v>
+        <v>-7.875457875457</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D26" s="14">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="E26" s="15">
-        <v>3.448275862068</v>
+        <v>37.142857142857</v>
       </c>
       <c r="F26" s="14">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="G26" s="14">
         <v>340</v>
       </c>
       <c r="H26" s="15">
-        <v>8.823529411764</v>
+        <v>10.588235294117</v>
       </c>
       <c r="I26" s="14">
-        <v>1224</v>
+        <v>1319</v>
       </c>
       <c r="J26" s="14">
-        <v>1217</v>
+        <v>1287</v>
       </c>
       <c r="K26" s="15">
-        <v>0.575184880854</v>
+        <v>2.486402486402</v>
       </c>
       <c r="L26" s="15">
-        <v>0</v>
+        <v>-0.302343159486</v>
       </c>
       <c r="M26" s="15">
-        <v>1.661129568106</v>
+        <v>2.168861347792</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E27" s="15">
-        <v>133.333333333333</v>
+        <v>160</v>
       </c>
       <c r="F27" s="14">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G27" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H27" s="15">
-        <v>70.588235294117</v>
+        <v>160</v>
       </c>
       <c r="I27" s="14">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="J27" s="14">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="K27" s="15">
-        <v>31.25</v>
+        <v>43.478260869565</v>
       </c>
       <c r="L27" s="15">
-        <v>12</v>
+        <v>22.222222222222</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>7</v>
       </c>
       <c r="D28" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E28" s="15">
-        <v>-12.5</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F28" s="14">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G28" s="14">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H28" s="15">
-        <v>10.526315789473</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="I28" s="14">
+        <v>143</v>
+      </c>
+      <c r="J28" s="14">
         <v>138</v>
       </c>
-      <c r="J28" s="14">
-        <v>127</v>
-      </c>
       <c r="K28" s="15">
-        <v>8.661417322834</v>
+        <v>3.623188405797</v>
       </c>
       <c r="L28" s="15">
-        <v>33.980582524271</v>
+        <v>25.438596491228</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1485,22 +1485,22 @@
         <v>400</v>
       </c>
       <c r="I29" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J29" s="14">
         <v>18</v>
       </c>
       <c r="K29" s="15">
-        <v>-33.333333333333</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="L29" s="15">
-        <v>-52</v>
+        <v>-55.172413793103</v>
       </c>
       <c r="M29" s="15">
-        <v>-77.358490566037</v>
+        <v>-76.363636363636</v>
       </c>
       <c r="N29" s="15">
-        <v>-91.489361702127</v>
+        <v>-91.719745222929</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1526,57 +1526,57 @@
         <v>400</v>
       </c>
       <c r="I30" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J30" s="14">
         <v>9</v>
       </c>
       <c r="K30" s="15">
-        <v>33.333333333333</v>
+        <v>44.444444444444</v>
       </c>
       <c r="L30" s="15">
-        <v>-47.826086956521</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-72.093023255813</v>
+        <v>-71.111111111111</v>
       </c>
       <c r="N30" s="15">
-        <v>-90.476190476190</v>
+        <v>-90.845070422535</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="C31" s="14">
+        <v>1</v>
+      </c>
+      <c r="D31" s="14">
+        <v>2</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-50</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I31" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J31" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K31" s="15">
-        <v>85.714285714285</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L31" s="15">
-        <v>44.444444444444</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1607,35 +1607,35 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
+      </c>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>0</v>
+      </c>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H33" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I33" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J33" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K33" s="15">
-        <v>-42.857142857142</v>
+        <v>-37.5</v>
       </c>
       <c r="L33" s="15">
-        <v>-55.555555555555</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-pbqs.xlsx
+++ b/data/source/weekly/cs-en-us-pbqs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -861,31 +861,31 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>4</v>
-      </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>300</v>
+        <v>3</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J14" s="14">
         <v>11</v>
       </c>
       <c r="K14" s="15">
-        <v>9.090909090909</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L14" s="15">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M14" s="15">
-        <v>-36.842105263157</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="N14" s="15">
-        <v>-75.510204081632</v>
+        <v>-74</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
+        <v>4</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>300</v>
+      </c>
+      <c r="F15" s="14">
+        <v>27</v>
+      </c>
+      <c r="G15" s="14">
         <v>10</v>
       </c>
-      <c r="D15" s="14">
-        <v>4</v>
-      </c>
-      <c r="E15" s="15">
-        <v>150</v>
-      </c>
-      <c r="F15" s="14">
-        <v>31</v>
-      </c>
-      <c r="G15" s="14">
-        <v>11</v>
-      </c>
       <c r="H15" s="15">
-        <v>181.818181818182</v>
+        <v>170</v>
       </c>
       <c r="I15" s="14">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J15" s="14">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K15" s="15">
-        <v>37.037037037037</v>
+        <v>41.818181818181</v>
       </c>
       <c r="L15" s="15">
-        <v>39.622641509434</v>
+        <v>36.842105263157</v>
       </c>
       <c r="M15" s="15">
-        <v>111.428571428571</v>
+        <v>105.263157894737</v>
       </c>
       <c r="N15" s="15">
-        <v>-26.732673267326</v>
+        <v>-27.777777777777</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D16" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E16" s="15">
-        <v>17.647058823529</v>
+        <v>10.526315789473</v>
       </c>
       <c r="F16" s="14">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G16" s="14">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H16" s="15">
-        <v>16.883116883116</v>
+        <v>24</v>
       </c>
       <c r="I16" s="14">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="J16" s="14">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="K16" s="15">
-        <v>4.166666666666</v>
+        <v>5.135951661631</v>
       </c>
       <c r="L16" s="15">
-        <v>-12.868632707774</v>
+        <v>-13.432835820895</v>
       </c>
       <c r="M16" s="15">
-        <v>-47.154471544715</v>
+        <v>-47.031963470319</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.471613768439</v>
+        <v>-85.353535353535</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D17" s="14">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="E17" s="15">
-        <v>39.024390243902</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="F17" s="14">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G17" s="14">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="H17" s="15">
-        <v>25</v>
+        <v>11.059907834101</v>
       </c>
       <c r="I17" s="14">
-        <v>856</v>
+        <v>917</v>
       </c>
       <c r="J17" s="14">
-        <v>813</v>
+        <v>878</v>
       </c>
       <c r="K17" s="15">
-        <v>5.289052890528</v>
+        <v>4.441913439635</v>
       </c>
       <c r="L17" s="15">
-        <v>-2.947845804988</v>
+        <v>-3.167898627243</v>
       </c>
       <c r="M17" s="15">
-        <v>86.899563318777</v>
+        <v>87.142857142857</v>
       </c>
       <c r="N17" s="15">
-        <v>-11.387163561076</v>
+        <v>-11.742059672762</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D18" s="14">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E18" s="15">
-        <v>66.666666666666</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="F18" s="14">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G18" s="14">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H18" s="15">
-        <v>-6.024096385542</v>
+        <v>-4</v>
       </c>
       <c r="I18" s="14">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="J18" s="14">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="K18" s="15">
-        <v>-27.8125</v>
+        <v>-27.192982456140</v>
       </c>
       <c r="L18" s="15">
-        <v>-23.255813953488</v>
+        <v>-23.619631901840</v>
       </c>
       <c r="M18" s="15">
-        <v>-58.896797153024</v>
+        <v>-57.796610169491</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.142638036809</v>
+        <v>-91.113490364025</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="D19" s="14">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E19" s="15">
-        <v>35.593220338983</v>
+        <v>47.619047619047</v>
       </c>
       <c r="F19" s="14">
-        <v>291</v>
+        <v>323</v>
       </c>
       <c r="G19" s="14">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="H19" s="15">
-        <v>23.829787234042</v>
+        <v>41.048034934497</v>
       </c>
       <c r="I19" s="14">
-        <v>1024</v>
+        <v>1122</v>
       </c>
       <c r="J19" s="14">
-        <v>885</v>
+        <v>948</v>
       </c>
       <c r="K19" s="15">
-        <v>15.706214689265</v>
+        <v>18.354430379746</v>
       </c>
       <c r="L19" s="15">
-        <v>0.886699507389</v>
+        <v>4.372093023255</v>
       </c>
       <c r="M19" s="15">
-        <v>27.680798004987</v>
+        <v>30.011587485515</v>
       </c>
       <c r="N19" s="15">
-        <v>-47.808358817533</v>
+        <v>-48.294930875576</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>31</v>
       </c>
       <c r="D20" s="14">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E20" s="15">
-        <v>-26.190476190476</v>
+        <v>-18.421052631578</v>
       </c>
       <c r="F20" s="14">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G20" s="14">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H20" s="15">
-        <v>-16.993464052287</v>
+        <v>-14.569536423841</v>
       </c>
       <c r="I20" s="14">
-        <v>484</v>
+        <v>513</v>
       </c>
       <c r="J20" s="14">
-        <v>529</v>
+        <v>568</v>
       </c>
       <c r="K20" s="15">
-        <v>-8.506616257088</v>
+        <v>-9.683098591549</v>
       </c>
       <c r="L20" s="15">
-        <v>-10.865561694291</v>
+        <v>-11.398963730569</v>
       </c>
       <c r="M20" s="15">
-        <v>0.414937759336</v>
+        <v>-0.388349514563</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.551754232850</v>
+        <v>-91.598427775958</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D21" s="17">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="E21" s="18">
-        <v>25.142857142857</v>
+        <v>6.25</v>
       </c>
       <c r="F21" s="17">
-        <v>861</v>
+        <v>888</v>
       </c>
       <c r="G21" s="17">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="H21" s="18">
-        <v>14.494680851063</v>
+        <v>17.305151915455</v>
       </c>
       <c r="I21" s="17">
-        <v>3006</v>
+        <v>3240</v>
       </c>
       <c r="J21" s="17">
-        <v>2924</v>
+        <v>3133</v>
       </c>
       <c r="K21" s="18">
-        <v>2.804377564979</v>
+        <v>3.415256942227</v>
       </c>
       <c r="L21" s="18">
-        <v>-5.382436260623</v>
+        <v>-4.593639575971</v>
       </c>
       <c r="M21" s="18">
-        <v>1.109989909182</v>
+        <v>2.143757881462</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.981248168766</v>
+        <v>-77.885468568698</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F22" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G22" s="14">
         <v>7</v>
       </c>
       <c r="H22" s="15">
-        <v>57.142857142857</v>
+        <v>85.714285714285</v>
       </c>
       <c r="I22" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J22" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K22" s="15">
-        <v>104.761904761905</v>
+        <v>91.666666666666</v>
       </c>
       <c r="L22" s="15">
-        <v>7.5</v>
+        <v>6.976744186046</v>
       </c>
       <c r="M22" s="15">
-        <v>19.444444444444</v>
+        <v>24.324324324324</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>50</v>
+        <v>-40</v>
       </c>
       <c r="F23" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G23" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H23" s="15">
-        <v>157.142857142857</v>
+        <v>54.545454545454</v>
       </c>
       <c r="I23" s="14">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J23" s="14">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K23" s="15">
-        <v>-14.516129032258</v>
+        <v>-14.925373134328</v>
       </c>
       <c r="L23" s="15">
-        <v>-14.516129032258</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="M23" s="15">
-        <v>6</v>
+        <v>7.547169811320</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D24" s="14">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E24" s="15">
-        <v>-9.183673469387</v>
+        <v>-4.663212435233</v>
       </c>
       <c r="F24" s="14">
-        <v>741</v>
+        <v>757</v>
       </c>
       <c r="G24" s="14">
-        <v>658</v>
+        <v>685</v>
       </c>
       <c r="H24" s="15">
-        <v>12.613981762917</v>
+        <v>10.510948905109</v>
       </c>
       <c r="I24" s="14">
-        <v>2666</v>
+        <v>2848</v>
       </c>
       <c r="J24" s="14">
-        <v>2536</v>
+        <v>2729</v>
       </c>
       <c r="K24" s="15">
-        <v>5.126182965299</v>
+        <v>4.360571637962</v>
       </c>
       <c r="L24" s="15">
-        <v>-1.623616236162</v>
+        <v>-0.628053035589</v>
       </c>
       <c r="M24" s="15">
-        <v>59.069212410501</v>
+        <v>56.828193832599</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="D25" s="14">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="E25" s="15">
-        <v>-31.313131313131</v>
+        <v>3.658536585365</v>
       </c>
       <c r="F25" s="14">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="G25" s="14">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="H25" s="15">
-        <v>-6.101694915254</v>
+        <v>-4</v>
       </c>
       <c r="I25" s="14">
-        <v>1006</v>
+        <v>1093</v>
       </c>
       <c r="J25" s="14">
-        <v>1062</v>
+        <v>1144</v>
       </c>
       <c r="K25" s="15">
-        <v>-5.273069679849</v>
+        <v>-4.458041958041</v>
       </c>
       <c r="L25" s="15">
-        <v>-7.875457875457</v>
+        <v>-4.956521739130</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D26" s="14">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="E26" s="15">
-        <v>37.142857142857</v>
+        <v>-7.547169811320</v>
       </c>
       <c r="F26" s="14">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="G26" s="14">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="H26" s="15">
-        <v>10.588235294117</v>
+        <v>9.550561797752</v>
       </c>
       <c r="I26" s="14">
-        <v>1319</v>
+        <v>1416</v>
       </c>
       <c r="J26" s="14">
-        <v>1287</v>
+        <v>1393</v>
       </c>
       <c r="K26" s="15">
-        <v>2.486402486402</v>
+        <v>1.651112706389</v>
       </c>
       <c r="L26" s="15">
-        <v>-0.302343159486</v>
+        <v>0.711237553342</v>
       </c>
       <c r="M26" s="15">
-        <v>2.168861347792</v>
+        <v>2.312138728323</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D27" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="F27" s="14">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G27" s="14">
         <v>15</v>
       </c>
       <c r="H27" s="15">
-        <v>160</v>
+        <v>113.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J27" s="14">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K27" s="15">
-        <v>43.478260869565</v>
+        <v>45.070422535211</v>
       </c>
       <c r="L27" s="15">
-        <v>22.222222222222</v>
+        <v>15.730337078651</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D28" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E28" s="15">
-        <v>-36.363636363636</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F28" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G28" s="14">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H28" s="15">
-        <v>-5.882352941176</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="J28" s="14">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="K28" s="15">
-        <v>3.623188405797</v>
+        <v>6.944444444444</v>
       </c>
       <c r="L28" s="15">
-        <v>25.438596491228</v>
+        <v>29.411764705882</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0</v>
       </c>
       <c r="F29" s="14">
         <v>5</v>
@@ -1485,22 +1485,22 @@
         <v>400</v>
       </c>
       <c r="I29" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J29" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K29" s="15">
-        <v>-27.777777777777</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="L29" s="15">
-        <v>-55.172413793103</v>
+        <v>-51.724137931034</v>
       </c>
       <c r="M29" s="15">
-        <v>-76.363636363636</v>
+        <v>-75.438596491228</v>
       </c>
       <c r="N29" s="15">
-        <v>-91.719745222929</v>
+        <v>-91.411042944785</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
       </c>
       <c r="F30" s="14">
         <v>5</v>
@@ -1526,36 +1526,36 @@
         <v>400</v>
       </c>
       <c r="I30" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J30" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K30" s="15">
-        <v>44.444444444444</v>
+        <v>40</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="M30" s="15">
-        <v>-71.111111111111</v>
+        <v>-70.212765957446</v>
       </c>
       <c r="N30" s="15">
-        <v>-90.845070422535</v>
+        <v>-90.540540540540</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="14">
         <v>1</v>
       </c>
-      <c r="D31" s="14">
-        <v>2</v>
-      </c>
       <c r="E31" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>3</v>
@@ -1567,16 +1567,16 @@
         <v>0</v>
       </c>
       <c r="I31" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J31" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K31" s="15">
-        <v>66.666666666666</v>
+        <v>60</v>
       </c>
       <c r="L31" s="15">
-        <v>66.666666666666</v>
+        <v>60</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1607,32 +1607,32 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E33" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
       </c>
       <c r="G33" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H33" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="I33" s="14">
         <v>5</v>
       </c>
       <c r="J33" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K33" s="15">
-        <v>-37.5</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="L33" s="15">
         <v>-44.444444444444</v>

--- a/data/source/weekly/cs-en-us-pbqs.xlsx
+++ b/data/source/weekly/cs-en-us-pbqs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -879,13 +879,13 @@
         <v>18.181818181818</v>
       </c>
       <c r="L14" s="15">
-        <v>30</v>
+        <v>18.181818181818</v>
       </c>
       <c r="M14" s="15">
-        <v>-31.578947368421</v>
+        <v>-35</v>
       </c>
       <c r="N14" s="15">
-        <v>-74</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E15" s="15">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="F15" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G15" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H15" s="15">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J15" s="14">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="K15" s="15">
-        <v>41.818181818181</v>
+        <v>40.983606557377</v>
       </c>
       <c r="L15" s="15">
-        <v>36.842105263157</v>
+        <v>48.275862068965</v>
       </c>
       <c r="M15" s="15">
-        <v>105.263157894737</v>
+        <v>95.454545454545</v>
       </c>
       <c r="N15" s="15">
-        <v>-27.777777777777</v>
+        <v>-22.522522522522</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D16" s="14">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E16" s="15">
-        <v>10.526315789473</v>
+        <v>12.903225806451</v>
       </c>
       <c r="F16" s="14">
+        <v>102</v>
+      </c>
+      <c r="G16" s="14">
         <v>93</v>
       </c>
-      <c r="G16" s="14">
-        <v>75</v>
-      </c>
       <c r="H16" s="15">
-        <v>24</v>
+        <v>9.677419354838</v>
       </c>
       <c r="I16" s="14">
-        <v>348</v>
+        <v>382</v>
       </c>
       <c r="J16" s="14">
-        <v>331</v>
+        <v>362</v>
       </c>
       <c r="K16" s="15">
-        <v>5.135951661631</v>
+        <v>5.524861878453</v>
       </c>
       <c r="L16" s="15">
-        <v>-13.432835820895</v>
+        <v>-12.385321100917</v>
       </c>
       <c r="M16" s="15">
-        <v>-47.031963470319</v>
+        <v>-44.070278184480</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.353535353535</v>
+        <v>-84.621578099839</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D17" s="14">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E17" s="15">
-        <v>-15.384615384615</v>
+        <v>-26.760563380281</v>
       </c>
       <c r="F17" s="14">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="G17" s="14">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="H17" s="15">
-        <v>11.059907834101</v>
+        <v>-3.829787234042</v>
       </c>
       <c r="I17" s="14">
-        <v>917</v>
+        <v>971</v>
       </c>
       <c r="J17" s="14">
-        <v>878</v>
+        <v>949</v>
       </c>
       <c r="K17" s="15">
-        <v>4.441913439635</v>
+        <v>2.318229715489</v>
       </c>
       <c r="L17" s="15">
-        <v>-3.167898627243</v>
+        <v>-2.997002997003</v>
       </c>
       <c r="M17" s="15">
-        <v>87.142857142857</v>
+        <v>88.178294573643</v>
       </c>
       <c r="N17" s="15">
-        <v>-11.742059672762</v>
+        <v>-12.522522522522</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D18" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E18" s="15">
-        <v>-22.727272727272</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F18" s="14">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G18" s="14">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H18" s="15">
-        <v>-4</v>
+        <v>-6.329113924050</v>
       </c>
       <c r="I18" s="14">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="J18" s="14">
-        <v>342</v>
+        <v>369</v>
       </c>
       <c r="K18" s="15">
-        <v>-27.192982456140</v>
+        <v>-28.184281842818</v>
       </c>
       <c r="L18" s="15">
-        <v>-23.619631901840</v>
+        <v>-24.501424501424</v>
       </c>
       <c r="M18" s="15">
-        <v>-57.796610169491</v>
+        <v>-57.735247208931</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.113490364025</v>
+        <v>-91.083445491251</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="D19" s="14">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="E19" s="15">
-        <v>47.619047619047</v>
+        <v>-23.376623376623</v>
       </c>
       <c r="F19" s="14">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="G19" s="14">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="H19" s="15">
-        <v>41.048034934497</v>
+        <v>24.603174603174</v>
       </c>
       <c r="I19" s="14">
-        <v>1122</v>
+        <v>1188</v>
       </c>
       <c r="J19" s="14">
-        <v>948</v>
+        <v>1025</v>
       </c>
       <c r="K19" s="15">
-        <v>18.354430379746</v>
+        <v>15.902439024390</v>
       </c>
       <c r="L19" s="15">
-        <v>4.372093023255</v>
+        <v>4.302019315188</v>
       </c>
       <c r="M19" s="15">
-        <v>30.011587485515</v>
+        <v>29.552889858233</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.294930875576</v>
+        <v>-49.618320610687</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>31</v>
       </c>
       <c r="D20" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E20" s="15">
-        <v>-18.421052631578</v>
+        <v>-22.5</v>
       </c>
       <c r="F20" s="14">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="G20" s="14">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="H20" s="15">
-        <v>-14.569536423841</v>
+        <v>-26.25</v>
       </c>
       <c r="I20" s="14">
-        <v>513</v>
+        <v>546</v>
       </c>
       <c r="J20" s="14">
-        <v>568</v>
+        <v>608</v>
       </c>
       <c r="K20" s="15">
-        <v>-9.683098591549</v>
+        <v>-10.197368421052</v>
       </c>
       <c r="L20" s="15">
-        <v>-11.398963730569</v>
+        <v>-10.049423393739</v>
       </c>
       <c r="M20" s="15">
-        <v>-0.388349514563</v>
+        <v>1.675977653631</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.598427775958</v>
+        <v>-91.566265060241</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="D21" s="17">
-        <v>208</v>
+        <v>252</v>
       </c>
       <c r="E21" s="18">
-        <v>6.25</v>
+        <v>-20.238095238095</v>
       </c>
       <c r="F21" s="17">
-        <v>888</v>
+        <v>865</v>
       </c>
       <c r="G21" s="17">
-        <v>757</v>
+        <v>833</v>
       </c>
       <c r="H21" s="18">
-        <v>17.305151915455</v>
+        <v>3.841536614645</v>
       </c>
       <c r="I21" s="17">
-        <v>3240</v>
+        <v>3451</v>
       </c>
       <c r="J21" s="17">
-        <v>3133</v>
+        <v>3385</v>
       </c>
       <c r="K21" s="18">
-        <v>3.415256942227</v>
+        <v>1.949778434268</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.593639575971</v>
+        <v>-4.218706633361</v>
       </c>
       <c r="M21" s="18">
-        <v>2.143757881462</v>
+        <v>3.199760765550</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.885468568698</v>
+        <v>-77.822762033288</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F22" s="14">
         <v>13</v>
       </c>
       <c r="G22" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H22" s="15">
-        <v>85.714285714285</v>
+        <v>30</v>
       </c>
       <c r="I22" s="14">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J22" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K22" s="15">
-        <v>91.666666666666</v>
+        <v>67.857142857142</v>
       </c>
       <c r="L22" s="15">
-        <v>6.976744186046</v>
+        <v>6.818181818181</v>
       </c>
       <c r="M22" s="15">
-        <v>24.324324324324</v>
+        <v>17.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E23" s="15">
-        <v>-40</v>
+        <v>-87.5</v>
       </c>
       <c r="F23" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G23" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H23" s="15">
-        <v>54.545454545454</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J23" s="14">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="K23" s="15">
-        <v>-14.925373134328</v>
+        <v>-22.666666666666</v>
       </c>
       <c r="L23" s="15">
-        <v>-13.636363636363</v>
+        <v>-15.942028985507</v>
       </c>
       <c r="M23" s="15">
-        <v>7.547169811320</v>
+        <v>3.571428571428</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>184</v>
+        <v>148</v>
       </c>
       <c r="D24" s="14">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="E24" s="15">
-        <v>-4.663212435233</v>
+        <v>-14.942528735632</v>
       </c>
       <c r="F24" s="14">
-        <v>757</v>
+        <v>677</v>
       </c>
       <c r="G24" s="14">
-        <v>685</v>
+        <v>694</v>
       </c>
       <c r="H24" s="15">
-        <v>10.510948905109</v>
+        <v>-2.449567723342</v>
       </c>
       <c r="I24" s="14">
-        <v>2848</v>
+        <v>2992</v>
       </c>
       <c r="J24" s="14">
-        <v>2729</v>
+        <v>2903</v>
       </c>
       <c r="K24" s="15">
-        <v>4.360571637962</v>
+        <v>3.065794006200</v>
       </c>
       <c r="L24" s="15">
-        <v>-0.628053035589</v>
+        <v>-1.675977653631</v>
       </c>
       <c r="M24" s="15">
-        <v>56.828193832599</v>
+        <v>54.945624029000</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="D25" s="14">
         <v>82</v>
       </c>
       <c r="E25" s="15">
-        <v>3.658536585365</v>
+        <v>-47.560975609756</v>
       </c>
       <c r="F25" s="14">
-        <v>288</v>
+        <v>243</v>
       </c>
       <c r="G25" s="14">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="H25" s="15">
-        <v>-4</v>
+        <v>-23.584905660377</v>
       </c>
       <c r="I25" s="14">
-        <v>1093</v>
+        <v>1136</v>
       </c>
       <c r="J25" s="14">
-        <v>1144</v>
+        <v>1226</v>
       </c>
       <c r="K25" s="15">
-        <v>-4.458041958041</v>
+        <v>-7.340946166394</v>
       </c>
       <c r="L25" s="15">
-        <v>-4.956521739130</v>
+        <v>-8.016194331983</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D26" s="14">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E26" s="15">
-        <v>-7.547169811320</v>
+        <v>-19.469026548672</v>
       </c>
       <c r="F26" s="14">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="G26" s="14">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="H26" s="15">
-        <v>9.550561797752</v>
+        <v>1.063829787234</v>
       </c>
       <c r="I26" s="14">
-        <v>1416</v>
+        <v>1509</v>
       </c>
       <c r="J26" s="14">
-        <v>1393</v>
+        <v>1506</v>
       </c>
       <c r="K26" s="15">
-        <v>1.651112706389</v>
+        <v>0.199203187250</v>
       </c>
       <c r="L26" s="15">
-        <v>0.711237553342</v>
+        <v>-1.178781925343</v>
       </c>
       <c r="M26" s="15">
-        <v>2.312138728323</v>
+        <v>2.374491180461</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E27" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F27" s="14">
         <v>32</v>
       </c>
       <c r="G27" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H27" s="15">
-        <v>113.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="J27" s="14">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="K27" s="15">
-        <v>45.070422535211</v>
+        <v>44.155844155844</v>
       </c>
       <c r="L27" s="15">
-        <v>15.730337078651</v>
+        <v>21.978021978022</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>17</v>
+      </c>
+      <c r="D28" s="14">
         <v>11</v>
       </c>
-      <c r="D28" s="14">
-        <v>6</v>
-      </c>
       <c r="E28" s="15">
-        <v>83.333333333333</v>
+        <v>54.545454545454</v>
       </c>
       <c r="F28" s="14">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G28" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>13.888888888888</v>
       </c>
       <c r="I28" s="14">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="J28" s="14">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="K28" s="15">
-        <v>6.944444444444</v>
+        <v>9.032258064516</v>
       </c>
       <c r="L28" s="15">
-        <v>29.411764705882</v>
+        <v>28.030303030303</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1467,40 +1467,40 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" s="14">
         <v>1</v>
       </c>
       <c r="E29" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F29" s="14">
         <v>5</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="I29" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J29" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K29" s="15">
-        <v>-26.315789473684</v>
+        <v>-20</v>
       </c>
       <c r="L29" s="15">
-        <v>-51.724137931034</v>
+        <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>-75.438596491228</v>
+        <v>-72.881355932203</v>
       </c>
       <c r="N29" s="15">
-        <v>-91.411042944785</v>
+        <v>-90.697674418604</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,40 +1508,40 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" s="14">
         <v>1</v>
       </c>
       <c r="E30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F30" s="14">
         <v>5</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="I30" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J30" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K30" s="15">
-        <v>40</v>
+        <v>45.454545454545</v>
       </c>
       <c r="L30" s="15">
-        <v>-46.153846153846</v>
+        <v>-44.827586206896</v>
       </c>
       <c r="M30" s="15">
-        <v>-70.212765957446</v>
+        <v>-67.346938775510</v>
       </c>
       <c r="N30" s="15">
-        <v>-90.540540540540</v>
+        <v>-89.677419354838</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31" s="14">
         <v>3</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I31" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J31" s="14">
         <v>10</v>
       </c>
       <c r="K31" s="15">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="L31" s="15">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>3</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-pbqs.xlsx
+++ b/data/source/weekly/cs-en-us-pbqs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -861,7 +861,7 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -879,13 +879,13 @@
         <v>18.181818181818</v>
       </c>
       <c r="L14" s="15">
-        <v>18.181818181818</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M14" s="15">
-        <v>-35</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="N14" s="15">
-        <v>-75</v>
+        <v>-75.925925925925</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
+        <v>4</v>
+      </c>
+      <c r="D15" s="14">
         <v>9</v>
       </c>
-      <c r="D15" s="14">
-        <v>6</v>
-      </c>
       <c r="E15" s="15">
-        <v>50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F15" s="14">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G15" s="14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I15" s="14">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="J15" s="14">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="K15" s="15">
-        <v>40.983606557377</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L15" s="15">
-        <v>48.275862068965</v>
+        <v>47.540983606557</v>
       </c>
       <c r="M15" s="15">
-        <v>95.454545454545</v>
+        <v>104.545454545455</v>
       </c>
       <c r="N15" s="15">
-        <v>-22.522522522522</v>
+        <v>-25.619834710743</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E16" s="15">
-        <v>12.903225806451</v>
+        <v>-31.034482758620</v>
       </c>
       <c r="F16" s="14">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G16" s="14">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H16" s="15">
-        <v>9.677419354838</v>
+        <v>2.083333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="J16" s="14">
-        <v>362</v>
+        <v>391</v>
       </c>
       <c r="K16" s="15">
-        <v>5.524861878453</v>
+        <v>2.813299232736</v>
       </c>
       <c r="L16" s="15">
-        <v>-12.385321100917</v>
+        <v>-12.798264642082</v>
       </c>
       <c r="M16" s="15">
-        <v>-44.070278184480</v>
+        <v>-44.704264099037</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.621578099839</v>
+        <v>-84.550345887778</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="D17" s="14">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E17" s="15">
-        <v>-26.760563380281</v>
+        <v>15.151515151515</v>
       </c>
       <c r="F17" s="14">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="G17" s="14">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H17" s="15">
-        <v>-3.829787234042</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>971</v>
+        <v>1048</v>
       </c>
       <c r="J17" s="14">
-        <v>949</v>
+        <v>1015</v>
       </c>
       <c r="K17" s="15">
-        <v>2.318229715489</v>
+        <v>3.251231527093</v>
       </c>
       <c r="L17" s="15">
-        <v>-2.997002997003</v>
+        <v>-3.142329020332</v>
       </c>
       <c r="M17" s="15">
-        <v>88.178294573643</v>
+        <v>93.357933579335</v>
       </c>
       <c r="N17" s="15">
-        <v>-12.522522522522</v>
+        <v>-11.486486486486</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D18" s="14">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E18" s="15">
-        <v>-44.444444444444</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="F18" s="14">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G18" s="14">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H18" s="15">
-        <v>-6.329113924050</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="I18" s="14">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="J18" s="14">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="K18" s="15">
-        <v>-28.184281842818</v>
+        <v>-28.497409326424</v>
       </c>
       <c r="L18" s="15">
-        <v>-24.501424501424</v>
+        <v>-23.545706371191</v>
       </c>
       <c r="M18" s="15">
-        <v>-57.735247208931</v>
+        <v>-58.496240601503</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.083445491251</v>
+        <v>-91.187739463601</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D19" s="14">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E19" s="15">
-        <v>-23.376623376623</v>
+        <v>-4.411764705882</v>
       </c>
       <c r="F19" s="14">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="G19" s="14">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="H19" s="15">
-        <v>24.603174603174</v>
+        <v>10.112359550561</v>
       </c>
       <c r="I19" s="14">
-        <v>1188</v>
+        <v>1256</v>
       </c>
       <c r="J19" s="14">
-        <v>1025</v>
+        <v>1093</v>
       </c>
       <c r="K19" s="15">
-        <v>15.902439024390</v>
+        <v>14.913083257090</v>
       </c>
       <c r="L19" s="15">
-        <v>4.302019315188</v>
+        <v>4.666666666666</v>
       </c>
       <c r="M19" s="15">
-        <v>29.552889858233</v>
+        <v>27.902240325865</v>
       </c>
       <c r="N19" s="15">
-        <v>-49.618320610687</v>
+        <v>-50.27711797308</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D20" s="14">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E20" s="15">
-        <v>-22.5</v>
+        <v>-19.148936170212</v>
       </c>
       <c r="F20" s="14">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="G20" s="14">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="H20" s="15">
-        <v>-26.25</v>
+        <v>-23.353293413173</v>
       </c>
       <c r="I20" s="14">
-        <v>546</v>
+        <v>583</v>
       </c>
       <c r="J20" s="14">
-        <v>608</v>
+        <v>655</v>
       </c>
       <c r="K20" s="15">
-        <v>-10.197368421052</v>
+        <v>-10.992366412213</v>
       </c>
       <c r="L20" s="15">
-        <v>-10.049423393739</v>
+        <v>-9.612403100775</v>
       </c>
       <c r="M20" s="15">
-        <v>1.675977653631</v>
+        <v>2.101576182136</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.566265060241</v>
+        <v>-91.462878898813</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="D21" s="17">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="E21" s="18">
-        <v>-20.238095238095</v>
+        <v>-8.898305084745</v>
       </c>
       <c r="F21" s="17">
-        <v>865</v>
+        <v>852</v>
       </c>
       <c r="G21" s="17">
-        <v>833</v>
+        <v>871</v>
       </c>
       <c r="H21" s="18">
-        <v>3.841536614645</v>
+        <v>-2.181400688863</v>
       </c>
       <c r="I21" s="17">
-        <v>3451</v>
+        <v>3668</v>
       </c>
       <c r="J21" s="17">
-        <v>3385</v>
+        <v>3621</v>
       </c>
       <c r="K21" s="18">
-        <v>1.949778434268</v>
+        <v>1.297983982325</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.218706633361</v>
+        <v>-4.079497907949</v>
       </c>
       <c r="M21" s="18">
-        <v>3.199760765550</v>
+        <v>3.236701379116</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.822762033288</v>
+        <v>-77.699416342412</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E22" s="15">
-        <v>-50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F22" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G22" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H22" s="15">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J22" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K22" s="15">
-        <v>67.857142857142</v>
+        <v>61.290322580645</v>
       </c>
       <c r="L22" s="15">
-        <v>6.818181818181</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M22" s="15">
-        <v>17.5</v>
+        <v>19.047619047619</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E23" s="15">
-        <v>-87.5</v>
+        <v>-70</v>
       </c>
       <c r="F23" s="14">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G23" s="14">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="I23" s="14">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J23" s="14">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K23" s="15">
-        <v>-22.666666666666</v>
+        <v>-28.235294117647</v>
       </c>
       <c r="L23" s="15">
-        <v>-15.942028985507</v>
+        <v>-18.666666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>3.571428571428</v>
+        <v>5.172413793103</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="D24" s="14">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="E24" s="15">
-        <v>-14.942528735632</v>
+        <v>-16.315789473684</v>
       </c>
       <c r="F24" s="14">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="G24" s="14">
-        <v>694</v>
+        <v>753</v>
       </c>
       <c r="H24" s="15">
-        <v>-2.449567723342</v>
+        <v>-10.889774236387</v>
       </c>
       <c r="I24" s="14">
-        <v>2992</v>
+        <v>3152</v>
       </c>
       <c r="J24" s="14">
-        <v>2903</v>
+        <v>3093</v>
       </c>
       <c r="K24" s="15">
-        <v>3.065794006200</v>
+        <v>1.907533139346</v>
       </c>
       <c r="L24" s="15">
-        <v>-1.675977653631</v>
+        <v>-1.714998440910</v>
       </c>
       <c r="M24" s="15">
-        <v>54.945624029000</v>
+        <v>51.175059952038</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D25" s="14">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E25" s="15">
-        <v>-47.560975609756</v>
+        <v>-44.047619047619</v>
       </c>
       <c r="F25" s="14">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G25" s="14">
-        <v>318</v>
+        <v>347</v>
       </c>
       <c r="H25" s="15">
-        <v>-23.584905660377</v>
+        <v>-29.682997118155</v>
       </c>
       <c r="I25" s="14">
-        <v>1136</v>
+        <v>1181</v>
       </c>
       <c r="J25" s="14">
-        <v>1226</v>
+        <v>1310</v>
       </c>
       <c r="K25" s="15">
-        <v>-7.340946166394</v>
+        <v>-9.847328244274</v>
       </c>
       <c r="L25" s="15">
-        <v>-8.016194331983</v>
+        <v>-9.709480122324</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>91</v>
       </c>
       <c r="D26" s="14">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="E26" s="15">
-        <v>-19.469026548672</v>
+        <v>2.247191011235</v>
       </c>
       <c r="F26" s="14">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="G26" s="14">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H26" s="15">
-        <v>1.063829787234</v>
+        <v>1.322751322751</v>
       </c>
       <c r="I26" s="14">
-        <v>1509</v>
+        <v>1603</v>
       </c>
       <c r="J26" s="14">
-        <v>1506</v>
+        <v>1595</v>
       </c>
       <c r="K26" s="15">
-        <v>0.199203187250</v>
+        <v>0.501567398119</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.178781925343</v>
+        <v>-0.927070457354</v>
       </c>
       <c r="M26" s="15">
-        <v>2.374491180461</v>
+        <v>2.166985340981</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>5</v>
+      </c>
+      <c r="D27" s="14">
         <v>9</v>
       </c>
-      <c r="D27" s="14">
-        <v>6</v>
-      </c>
       <c r="E27" s="15">
-        <v>50</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F27" s="14">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G27" s="14">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>31.818181818181</v>
       </c>
       <c r="I27" s="14">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="J27" s="14">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K27" s="15">
-        <v>44.155844155844</v>
+        <v>34.883720930232</v>
       </c>
       <c r="L27" s="15">
-        <v>21.978021978022</v>
+        <v>22.105263157894</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D28" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E28" s="15">
-        <v>54.545454545454</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F28" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G28" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H28" s="15">
-        <v>13.888888888888</v>
+        <v>13.513513513513</v>
       </c>
       <c r="I28" s="14">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="J28" s="14">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="K28" s="15">
-        <v>9.032258064516</v>
+        <v>7.317073170731</v>
       </c>
       <c r="L28" s="15">
-        <v>28.030303030303</v>
+        <v>26.618705035971</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>2</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
+        <v>3</v>
+      </c>
+      <c r="G29" s="14">
         <v>5</v>
       </c>
-      <c r="G29" s="14">
-        <v>2</v>
-      </c>
       <c r="H29" s="15">
-        <v>150</v>
+        <v>-40</v>
       </c>
       <c r="I29" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J29" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K29" s="15">
-        <v>-20</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="L29" s="15">
-        <v>-50</v>
+        <v>-62.5</v>
       </c>
       <c r="M29" s="15">
-        <v>-72.881355932203</v>
+        <v>-76.190476190476</v>
       </c>
       <c r="N29" s="15">
-        <v>-90.697674418604</v>
+        <v>-91.847826086956</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14">
         <v>2</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
       <c r="E30" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H30" s="15">
-        <v>150</v>
+        <v>-25</v>
       </c>
       <c r="I30" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J30" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K30" s="15">
-        <v>45.454545454545</v>
+        <v>15.384615384615</v>
       </c>
       <c r="L30" s="15">
-        <v>-44.827586206896</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="M30" s="15">
-        <v>-67.346938775510</v>
+        <v>-71.698113207547</v>
       </c>
       <c r="N30" s="15">
-        <v>-89.677419354838</v>
+        <v>-91.017964071856</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>3</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H31" s="15">
-        <v>33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I31" s="14">
         <v>17</v>
       </c>
       <c r="J31" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K31" s="15">
-        <v>70</v>
+        <v>30.769230769230</v>
       </c>
       <c r="L31" s="15">
-        <v>70</v>
+        <v>54.545454545454</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1617,25 +1617,25 @@
         <v>21</v>
       </c>
       <c r="F33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="14">
         <v>4</v>
       </c>
       <c r="H33" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I33" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J33" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K33" s="15">
-        <v>-54.545454545454</v>
+        <v>-40</v>
       </c>
       <c r="L33" s="15">
-        <v>-44.444444444444</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>
